--- a/data/2026 Bowler Chart - OFS Training.xlsx
+++ b/data/2026 Bowler Chart - OFS Training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212529239\AppData\Local\Box\Box Edit\Documents\Z0nl+M3vCk+t6PhhVzER4Q==\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\210077026\Box\OFS Global Technical Training @OFFICIAL NEW\Leadership Team\Bowler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{3E31836C-1E49-40FF-A81F-A1F905B5151F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{246048CA-BDDC-44E9-95CD-181E933AAAA5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767FFC3A-EA5D-4896-8768-4FAEF23DC63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="3120" windowWidth="29040" windowHeight="15720" tabRatio="601" xr2:uid="{8476BB21-6D10-4BB9-B6CE-FEFD481D0662}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="601" xr2:uid="{8476BB21-6D10-4BB9-B6CE-FEFD481D0662}"/>
   </bookViews>
   <sheets>
     <sheet name="Bowler L1 Training" sheetId="16" r:id="rId1"/>
@@ -46,10 +46,12 @@
     <author>tc={37C346EB-164E-421B-B3A5-A71619208C83}</author>
     <author>tc={160740E7-DFEB-4450-B5C5-A17286B215D6}</author>
     <author>Philip Ganssmann</author>
+    <author>tc={1AF062B2-D337-4E87-B548-0EB2DB830EEC}</author>
     <author>tc={50577B9E-D913-49BB-B91E-A5BD3E934319}</author>
     <author>tc={4A61949D-D058-4614-9CBE-136784BCC6E7}</author>
     <author>tc={40736F15-DF93-4810-BC49-A79E1FB56ED1}</author>
     <author>tc={F644D89E-1836-4B19-B5E0-2664B9B5862D}</author>
+    <author>tc={249040F4-BD6C-4879-B42F-2781C2CB4456}</author>
   </authors>
   <commentList>
     <comment ref="Q6" authorId="0" shapeId="0" xr:uid="{06BE996C-F791-4A9F-AA6D-EE2A8EE2F4C3}">
@@ -283,6 +285,14 @@
         </r>
       </text>
     </comment>
+    <comment ref="S33" authorId="6" shapeId="0" xr:uid="{1AF062B2-D337-4E87-B548-0EB2DB830EEC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ELT ST 26-1</t>
+      </text>
+    </comment>
     <comment ref="C34" authorId="1" shapeId="0" xr:uid="{508037C5-7575-470A-939A-71BD192D06EF}">
       <text>
         <r>
@@ -373,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O42" authorId="6" shapeId="0" xr:uid="{50577B9E-D913-49BB-B91E-A5BD3E934319}">
+    <comment ref="O42" authorId="7" shapeId="0" xr:uid="{50577B9E-D913-49BB-B91E-A5BD3E934319}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -458,7 +468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="7" shapeId="0" xr:uid="{4A61949D-D058-4614-9CBE-136784BCC6E7}">
+    <comment ref="K51" authorId="8" shapeId="0" xr:uid="{4A61949D-D058-4614-9CBE-136784BCC6E7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -468,7 +478,7 @@
 As tracking stabilizes and system issues are resolved, the data will more accurately reflect true performance and is expected to improve.</t>
       </text>
     </comment>
-    <comment ref="M51" authorId="8" shapeId="0" xr:uid="{40736F15-DF93-4810-BC49-A79E1FB56ED1}">
+    <comment ref="M51" authorId="9" shapeId="0" xr:uid="{40736F15-DF93-4810-BC49-A79E1FB56ED1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -476,12 +486,20 @@
     https://gevernova.box.com/s/17o8hpcpubfb6lm82c157gdcde9kcful</t>
       </text>
     </comment>
-    <comment ref="Q51" authorId="9" shapeId="0" xr:uid="{F644D89E-1836-4B19-B5E0-2664B9B5862D}">
+    <comment ref="Q51" authorId="10" shapeId="0" xr:uid="{F644D89E-1836-4B19-B5E0-2664B9B5862D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Ben Smith access issues</t>
+      </text>
+    </comment>
+    <comment ref="T51" authorId="11" shapeId="0" xr:uid="{249040F4-BD6C-4879-B42F-2781C2CB4456}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://gevernova.box.com/s/zfcjhwxq8my71tmkvyva54f2s0airatl</t>
       </text>
     </comment>
     <comment ref="C52" authorId="1" shapeId="0" xr:uid="{1D261BA2-8304-49D6-B2B0-DECA97456338}">
@@ -581,7 +599,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="116">
   <si>
     <t>Level 2</t>
   </si>
@@ -702,9 +720,6 @@
   </si>
   <si>
     <t>Daxer</t>
-  </si>
-  <si>
-    <t>Aug: OE Controls courses @ HLC w/ low rating because of AC and internet issues in building 3</t>
   </si>
   <si>
     <t># Exams Migrated to Xyleme</t>
@@ -827,7 +842,7 @@
     <t>Customer Training Sales</t>
   </si>
   <si>
-    <t>Apr low due to Service week</t>
+    <t>Trending low due to Iran crisis</t>
   </si>
   <si>
     <t>GP TrainingOrg Gross Margin</t>
@@ -956,17 +971,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\)"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00"/>
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1149,6 +1163,12 @@
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1351,7 +1371,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="236">
@@ -1441,13 +1461,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1457,7 +1477,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1519,9 +1539,6 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1540,22 +1557,22 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1576,7 +1593,7 @@
     <xf numFmtId="1" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,16 +1614,16 @@
     <xf numFmtId="9" fontId="6" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="28" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1621,7 +1638,7 @@
     <xf numFmtId="1" fontId="6" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="6" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1663,19 +1680,19 @@
     <xf numFmtId="1" fontId="28" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="28" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="28" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="9" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1687,365 +1704,368 @@
     <xf numFmtId="37" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="8" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="27" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="30" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="30" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="39" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2065,13 +2085,14 @@
   <person displayName="Jim Rosen" id="{5990F661-A3AB-41F4-AEAA-FE26C0B875A9}" userId="" providerId=""/>
   <person displayName="Lizlee Galley" id="{F0C1FE1F-CA66-453D-BCFC-7F99948C8DD5}" userId="" providerId=""/>
   <person displayName="Leonardo Monzo" id="{609B96A1-92B7-4C31-9E45-8215DF1B6B95}" userId="" providerId=""/>
+  <person displayName="Rosen, Jim M (GE Vernova)" id="{207828A5-0907-4FA1-8C71-CDCF46857015}" userId="S::210077026@ge.com::7e36ff5b-dad9-4cae-9842-ebbdead30345" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2109,7 +2130,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2215,7 +2236,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2357,7 +2378,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2383,6 +2404,9 @@
   <threadedComment ref="F13" dT="2024-05-21T17:14:25.01" personId="{F0C1FE1F-CA66-453D-BCFC-7F99948C8DD5}" id="{160740E7-DFEB-4450-B5C5-A17286B215D6}">
     <text>90% RA ATS closure rate all sites by YE</text>
   </threadedComment>
+  <threadedComment ref="S33" dT="2026-10-09T13:03:48.82" personId="{207828A5-0907-4FA1-8C71-CDCF46857015}" id="{1AF062B2-D337-4E87-B548-0EB2DB830EEC}">
+    <text>ELT ST 26-1</text>
+  </threadedComment>
   <threadedComment ref="O42" dT="2026-07-08T12:43:26.92" personId="{609B96A1-92B7-4C31-9E45-8215DF1B6B95}" id="{50577B9E-D913-49BB-B91E-A5BD3E934319}">
     <text>Pre-arranged with Lead Instructor, the whole GT Mechanical class won't have Pre-OJT</text>
   </threadedComment>
@@ -2397,6 +2421,15 @@
   <threadedComment ref="Q51" dT="2026-08-10T18:51:22.55" personId="{5990F661-A3AB-41F4-AEAA-FE26C0B875A9}" id="{F644D89E-1836-4B19-B5E0-2664B9B5862D}">
     <text>Ben Smith access issues</text>
   </threadedComment>
+  <threadedComment ref="T51" dT="2026-10-09T13:21:36.44" personId="{207828A5-0907-4FA1-8C71-CDCF46857015}" id="{249040F4-BD6C-4879-B42F-2781C2CB4456}">
+    <text>https://gevernova.box.com/s/zfcjhwxq8my71tmkvyva54f2s0airatl</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>3210079111</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="60" url="https://gevernova.box.com/s/zfcjhwxq8my71tmkvyva54f2s0airatl"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -2406,7 +2439,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y95"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" style="7" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" style="7" customWidth="1"/>
@@ -2428,7 +2461,7 @@
     <col min="25" max="16384" width="8.5703125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.6">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2454,31 +2487,31 @@
       <c r="W1" s="5"/>
       <c r="X1" s="6"/>
     </row>
-    <row r="2" spans="1:25" ht="18">
+    <row r="2" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="171">
+      <c r="I2" s="182">
         <v>2026</v>
       </c>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="172"/>
-      <c r="S2" s="172"/>
-      <c r="T2" s="172"/>
-      <c r="U2" s="172"/>
-      <c r="V2" s="172"/>
-      <c r="W2" s="172"/>
-      <c r="X2" s="173"/>
-    </row>
-    <row r="3" spans="1:25" ht="31.15">
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
+      <c r="L2" s="183"/>
+      <c r="M2" s="183"/>
+      <c r="N2" s="183"/>
+      <c r="O2" s="183"/>
+      <c r="P2" s="183"/>
+      <c r="Q2" s="183"/>
+      <c r="R2" s="183"/>
+      <c r="S2" s="183"/>
+      <c r="T2" s="183"/>
+      <c r="U2" s="183"/>
+      <c r="V2" s="183"/>
+      <c r="W2" s="183"/>
+      <c r="X2" s="184"/>
+    </row>
+    <row r="3" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="9" t="s">
         <v>1</v>
@@ -2548,24 +2581,24 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B4" s="193" t="s">
+    <row r="4" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="163" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="181" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="164" t="s">
+      <c r="D4" s="188" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="180">
+      <c r="E4" s="189">
         <f>SUM(L4,P4,T4,X4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="124">
-        <v>0</v>
-      </c>
-      <c r="G4" s="181">
+      <c r="F4" s="192">
+        <v>0</v>
+      </c>
+      <c r="G4" s="191">
         <f>SUM(L6,P6,T6,X6)</f>
         <v>1</v>
       </c>
@@ -2625,13 +2658,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B5" s="193"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="181"/>
+    <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="163"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="191"/>
       <c r="H5" s="11" t="s">
         <v>27</v>
       </c>
@@ -2688,46 +2721,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B6" s="193"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="181"/>
+    <row r="6" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="163"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="192"/>
+      <c r="G6" s="191"/>
       <c r="H6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="86">
-        <v>0</v>
-      </c>
-      <c r="J6" s="86">
-        <v>0</v>
-      </c>
-      <c r="K6" s="86">
-        <v>0</v>
-      </c>
-      <c r="L6" s="97">
+      <c r="I6" s="85">
+        <v>0</v>
+      </c>
+      <c r="J6" s="85">
+        <v>0</v>
+      </c>
+      <c r="K6" s="85">
+        <v>0</v>
+      </c>
+      <c r="L6" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M6" s="86">
-        <v>0</v>
-      </c>
-      <c r="N6" s="86">
-        <v>0</v>
-      </c>
-      <c r="O6" s="115">
-        <v>0</v>
-      </c>
-      <c r="P6" s="97">
+      <c r="M6" s="85">
+        <v>0</v>
+      </c>
+      <c r="N6" s="85">
+        <v>0</v>
+      </c>
+      <c r="O6" s="114">
+        <v>0</v>
+      </c>
+      <c r="P6" s="96">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="116">
+      <c r="Q6" s="115">
         <v>1</v>
       </c>
-      <c r="R6" s="86">
+      <c r="R6" s="85">
         <v>0</v>
       </c>
       <c r="S6" s="14"/>
@@ -2743,24 +2776,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B7" s="193"/>
-      <c r="C7" s="127" t="s">
+    <row r="7" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="163"/>
+      <c r="C7" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="128" t="s">
+      <c r="D7" s="171" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="165">
-        <v>0</v>
-      </c>
-      <c r="F7" s="182">
-        <v>0</v>
-      </c>
-      <c r="G7" s="234">
+      <c r="E7" s="203">
+        <v>0</v>
+      </c>
+      <c r="F7" s="193">
+        <v>0</v>
+      </c>
+      <c r="G7" s="196">
         <v>0.95</v>
       </c>
-      <c r="H7" s="121" t="s">
+      <c r="H7" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="15">
@@ -2812,14 +2845,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B8" s="193"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="166"/>
-      <c r="F8" s="182"/>
-      <c r="G8" s="234"/>
-      <c r="H8" s="121" t="s">
+    <row r="8" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="163"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="171"/>
+      <c r="E8" s="204"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="196"/>
+      <c r="H8" s="122" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="15">
@@ -2871,44 +2904,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B9" s="193"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="121" t="s">
+    <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="163"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="193"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="85">
-        <v>0</v>
-      </c>
-      <c r="J9" s="85">
-        <v>0</v>
-      </c>
-      <c r="K9" s="85">
-        <v>0</v>
-      </c>
-      <c r="L9" s="97">
-        <v>0</v>
-      </c>
-      <c r="M9" s="85">
-        <v>0</v>
-      </c>
-      <c r="N9" s="85">
-        <v>0</v>
-      </c>
-      <c r="O9" s="85">
-        <v>0</v>
-      </c>
-      <c r="P9" s="97">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="117">
+      <c r="I9" s="84">
+        <v>0</v>
+      </c>
+      <c r="J9" s="84">
+        <v>0</v>
+      </c>
+      <c r="K9" s="84">
+        <v>0</v>
+      </c>
+      <c r="L9" s="96">
+        <v>0</v>
+      </c>
+      <c r="M9" s="84">
+        <v>0</v>
+      </c>
+      <c r="N9" s="84">
+        <v>0</v>
+      </c>
+      <c r="O9" s="84">
+        <v>0</v>
+      </c>
+      <c r="P9" s="96">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="116">
         <v>1.089</v>
       </c>
-      <c r="R9" s="233">
+      <c r="R9" s="118">
         <v>0.95</v>
       </c>
       <c r="S9" s="45"/>
@@ -2918,23 +2951,23 @@
       <c r="W9" s="17"/>
       <c r="X9" s="16"/>
     </row>
-    <row r="10" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B10" s="193"/>
-      <c r="C10" s="178" t="s">
+    <row r="10" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="163"/>
+      <c r="C10" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="164" t="s">
+      <c r="D10" s="188" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="135">
+      <c r="E10" s="202">
         <f>SUM(L10,P10,T10,X10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="124">
+      <c r="F10" s="192">
         <f>SUM(L11,P11,T11,X11)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="180">
+      <c r="G10" s="189">
         <f>SUM(L12,P12,T12,X12)</f>
         <v>0</v>
       </c>
@@ -2994,13 +3027,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B11" s="193"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="135"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="180"/>
+    <row r="11" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="163"/>
+      <c r="C11" s="181"/>
+      <c r="D11" s="188"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="189"/>
       <c r="H11" s="11" t="s">
         <v>27</v>
       </c>
@@ -3057,46 +3090,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B12" s="193"/>
-      <c r="C12" s="178"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="180"/>
+    <row r="12" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="163"/>
+      <c r="C12" s="181"/>
+      <c r="D12" s="188"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="189"/>
       <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="86">
-        <v>0</v>
-      </c>
-      <c r="J12" s="86">
-        <v>0</v>
-      </c>
-      <c r="K12" s="86">
-        <v>0</v>
-      </c>
-      <c r="L12" s="97">
+      <c r="I12" s="85">
+        <v>0</v>
+      </c>
+      <c r="J12" s="85">
+        <v>0</v>
+      </c>
+      <c r="K12" s="85">
+        <v>0</v>
+      </c>
+      <c r="L12" s="96">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="86">
-        <v>0</v>
-      </c>
-      <c r="N12" s="86">
-        <v>0</v>
-      </c>
-      <c r="O12" s="86">
-        <v>0</v>
-      </c>
-      <c r="P12" s="97">
+      <c r="M12" s="85">
+        <v>0</v>
+      </c>
+      <c r="N12" s="85">
+        <v>0</v>
+      </c>
+      <c r="O12" s="85">
+        <v>0</v>
+      </c>
+      <c r="P12" s="96">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="86">
-        <v>0</v>
-      </c>
-      <c r="R12" s="86">
+      <c r="Q12" s="85">
+        <v>0</v>
+      </c>
+      <c r="R12" s="85">
         <v>0</v>
       </c>
       <c r="S12" s="14"/>
@@ -3112,24 +3145,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B13" s="193"/>
-      <c r="C13" s="127" t="s">
+    <row r="13" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="163"/>
+      <c r="C13" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="128" t="s">
+      <c r="D13" s="171" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="179">
+      <c r="E13" s="156">
         <v>1</v>
       </c>
-      <c r="F13" s="143">
-        <v>0.9</v>
-      </c>
-      <c r="G13" s="179">
-        <v>0.9</v>
-      </c>
-      <c r="H13" s="121" t="s">
+      <c r="F13" s="201">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="156">
+        <v>0.9</v>
+      </c>
+      <c r="H13" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I13" s="15" t="s">
@@ -3181,14 +3214,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B14" s="193"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="179"/>
-      <c r="F14" s="143"/>
-      <c r="G14" s="179"/>
-      <c r="H14" s="121" t="s">
+    <row r="14" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="163"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="201"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="122" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="38">
@@ -3200,7 +3233,7 @@
       <c r="K14" s="38">
         <v>0.9</v>
       </c>
-      <c r="L14" s="92">
+      <c r="L14" s="91">
         <v>0.9</v>
       </c>
       <c r="M14" s="38">
@@ -3240,44 +3273,44 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B15" s="193"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="179"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="179"/>
-      <c r="H15" s="121" t="s">
+    <row r="15" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="163"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="171"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="76">
-        <v>0.9</v>
-      </c>
-      <c r="J15" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="76" t="s">
+      <c r="I15" s="75">
+        <v>0.9</v>
+      </c>
+      <c r="J15" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="87">
-        <v>0.9</v>
-      </c>
-      <c r="M15" s="76">
-        <v>0.9</v>
-      </c>
-      <c r="N15" s="76">
-        <v>0.9</v>
-      </c>
-      <c r="O15" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="87">
-        <v>0.9</v>
-      </c>
-      <c r="Q15" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="76" t="s">
+      <c r="L15" s="86">
+        <v>0.9</v>
+      </c>
+      <c r="M15" s="75">
+        <v>0.9</v>
+      </c>
+      <c r="N15" s="75">
+        <v>0.9</v>
+      </c>
+      <c r="O15" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="86">
+        <v>0.9</v>
+      </c>
+      <c r="Q15" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="75" t="s">
         <v>32</v>
       </c>
       <c r="S15" s="47"/>
@@ -3287,24 +3320,24 @@
       <c r="W15" s="17"/>
       <c r="X15" s="16"/>
     </row>
-    <row r="16" spans="1:25" ht="18.75" customHeight="1">
-      <c r="B16" s="193"/>
-      <c r="C16" s="125" t="s">
+    <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="163"/>
+      <c r="C16" s="206" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="169" t="s">
+      <c r="D16" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="124" t="s">
+      <c r="E16" s="192" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="155">
-        <v>0.9</v>
-      </c>
-      <c r="G16" s="152">
+      <c r="F16" s="194">
+        <v>0.9</v>
+      </c>
+      <c r="G16" s="199">
         <v>0.95</v>
       </c>
-      <c r="H16" s="123" t="s">
+      <c r="H16" s="121" t="s">
         <v>26</v>
       </c>
       <c r="I16" s="19" t="s">
@@ -3359,14 +3392,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B17" s="193"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="169"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="155"/>
-      <c r="G17" s="152"/>
-      <c r="H17" s="123" t="s">
+    <row r="17" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="163"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="190"/>
+      <c r="E17" s="192"/>
+      <c r="F17" s="194"/>
+      <c r="G17" s="199"/>
+      <c r="H17" s="121" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="21">
@@ -3418,44 +3451,44 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="18" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B18" s="193"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="169"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="183"/>
-      <c r="G18" s="153"/>
-      <c r="H18" s="123" t="s">
+    <row r="18" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="163"/>
+      <c r="C18" s="164"/>
+      <c r="D18" s="190"/>
+      <c r="E18" s="192"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="84">
+      <c r="I18" s="83">
         <v>0.92300000000000004</v>
       </c>
-      <c r="J18" s="76">
-        <v>0.9</v>
-      </c>
-      <c r="K18" s="84">
+      <c r="J18" s="75">
+        <v>0.9</v>
+      </c>
+      <c r="K18" s="83">
         <v>0.92300000000000004</v>
       </c>
-      <c r="L18" s="93">
+      <c r="L18" s="92">
         <v>0.92</v>
       </c>
-      <c r="M18" s="84">
+      <c r="M18" s="83">
         <v>1</v>
       </c>
-      <c r="N18" s="84">
+      <c r="N18" s="83">
         <v>1</v>
       </c>
-      <c r="O18" s="103">
+      <c r="O18" s="102">
         <v>84.6</v>
       </c>
-      <c r="P18" s="93">
+      <c r="P18" s="92">
         <v>0.95</v>
       </c>
-      <c r="Q18" s="84">
+      <c r="Q18" s="83">
         <v>1</v>
       </c>
-      <c r="R18" s="118">
+      <c r="R18" s="117">
         <v>1</v>
       </c>
       <c r="S18" s="52"/>
@@ -3465,26 +3498,26 @@
       <c r="W18" s="53"/>
       <c r="X18" s="43"/>
     </row>
-    <row r="19" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B19" s="193" t="s">
+    <row r="19" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="127" t="s">
+      <c r="C19" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="128" t="s">
+      <c r="D19" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="129">
+      <c r="E19" s="219">
         <v>83</v>
       </c>
-      <c r="F19" s="141">
+      <c r="F19" s="229">
         <v>83</v>
       </c>
-      <c r="G19" s="129">
-        <v>83.2</v>
-      </c>
-      <c r="H19" s="121" t="s">
+      <c r="G19" s="219">
+        <v>84.4</v>
+      </c>
+      <c r="H19" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="55">
@@ -3536,14 +3569,14 @@
         <v>80.099999999999994</v>
       </c>
     </row>
-    <row r="20" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B20" s="193"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="142"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="121" t="s">
+    <row r="20" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="163"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="171"/>
+      <c r="E20" s="220"/>
+      <c r="F20" s="230"/>
+      <c r="G20" s="220"/>
+      <c r="H20" s="122" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="55">
@@ -3595,75 +3628,76 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B21" s="193"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="142"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="121" t="s">
+    <row r="21" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="163"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="171"/>
+      <c r="E21" s="220"/>
+      <c r="F21" s="230"/>
+      <c r="G21" s="220"/>
+      <c r="H21" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="74">
         <v>79</v>
       </c>
-      <c r="J21" s="83">
+      <c r="J21" s="82">
         <v>84</v>
       </c>
-      <c r="K21" s="83">
+      <c r="K21" s="82">
         <v>87</v>
       </c>
-      <c r="L21" s="89">
+      <c r="L21" s="88">
         <v>85</v>
       </c>
-      <c r="M21" s="75">
+      <c r="M21" s="74">
         <v>79</v>
       </c>
-      <c r="N21" s="104">
+      <c r="N21" s="103">
         <v>91</v>
       </c>
-      <c r="O21" s="75">
+      <c r="O21" s="74">
         <v>75.8</v>
       </c>
-      <c r="P21" s="89">
+      <c r="P21" s="88">
         <v>84.4</v>
       </c>
-      <c r="Q21" s="104">
+      <c r="Q21" s="103">
         <v>84.7</v>
       </c>
-      <c r="R21" s="75">
+      <c r="R21" s="74">
         <v>82.9</v>
       </c>
-      <c r="S21" s="57"/>
-      <c r="T21" s="57"/>
+      <c r="S21" s="103">
+        <v>91.3</v>
+      </c>
+      <c r="T21" s="88">
+        <v>86.2</v>
+      </c>
       <c r="U21" s="57"/>
       <c r="V21" s="57"/>
       <c r="W21" s="57"/>
       <c r="X21" s="44"/>
-      <c r="Y21" s="7" t="s">
+    </row>
+    <row r="22" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="163"/>
+      <c r="C22" s="206" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="2:25" ht="19.5" customHeight="1">
-      <c r="B22" s="193"/>
-      <c r="C22" s="125" t="s">
+      <c r="D22" s="207" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="168" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="170" t="s">
+      <c r="E22" s="208" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="124">
+      <c r="F22" s="192">
         <v>55</v>
       </c>
-      <c r="G22" s="135">
+      <c r="G22" s="202">
         <f>SUM(L24,P24,T24,X24)</f>
         <v>78</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="121" t="s">
         <v>26</v>
       </c>
       <c r="I22" s="24" t="s">
@@ -3718,14 +3752,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B23" s="193"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="169"/>
-      <c r="E23" s="170"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="123" t="s">
+    <row r="23" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="163"/>
+      <c r="C23" s="164"/>
+      <c r="D23" s="190"/>
+      <c r="E23" s="208"/>
+      <c r="F23" s="192"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="121" t="s">
         <v>27</v>
       </c>
       <c r="I23" s="12">
@@ -3777,79 +3811,79 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B24" s="193"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="169"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="123" t="s">
+    <row r="24" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="163"/>
+      <c r="C24" s="164"/>
+      <c r="D24" s="190"/>
+      <c r="E24" s="208"/>
+      <c r="F24" s="192"/>
+      <c r="G24" s="202"/>
+      <c r="H24" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="85">
+      <c r="I24" s="84">
         <v>2</v>
       </c>
-      <c r="J24" s="83">
+      <c r="J24" s="82">
         <v>5</v>
       </c>
-      <c r="K24" s="79">
+      <c r="K24" s="78">
         <v>3</v>
       </c>
-      <c r="L24" s="98">
+      <c r="L24" s="97">
         <v>10</v>
       </c>
-      <c r="M24" s="83">
+      <c r="M24" s="82">
         <v>24</v>
       </c>
-      <c r="N24" s="79">
+      <c r="N24" s="78">
         <v>3</v>
       </c>
-      <c r="O24" s="83">
+      <c r="O24" s="82">
         <v>19</v>
       </c>
-      <c r="P24" s="98">
+      <c r="P24" s="97">
         <f>SUM(M24:O24)</f>
         <v>46</v>
       </c>
-      <c r="Q24" s="83">
+      <c r="Q24" s="82">
         <v>20</v>
       </c>
-      <c r="R24" s="79">
+      <c r="R24" s="78">
         <v>2</v>
       </c>
-      <c r="S24" s="68"/>
-      <c r="T24" s="78">
+      <c r="S24" s="67"/>
+      <c r="T24" s="77">
         <f>SUM(Q24:S24)</f>
         <v>22</v>
       </c>
-      <c r="U24" s="68"/>
-      <c r="V24" s="68"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
       <c r="W24" s="19"/>
-      <c r="X24" s="78">
+      <c r="X24" s="77">
         <f>SUM(U24:W24)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:25" ht="19.5" customHeight="1">
-      <c r="B25" s="193"/>
-      <c r="C25" s="198" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="199" t="s">
+    <row r="25" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="163"/>
+      <c r="C25" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="200" t="s">
+      <c r="D25" s="170" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="172" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="201">
+      <c r="F25" s="173">
         <v>120</v>
       </c>
-      <c r="G25" s="202">
+      <c r="G25" s="174">
         <f>SUM(L27,P27,T27,X27)</f>
-        <v>46</v>
-      </c>
-      <c r="H25" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="15" t="s">
@@ -3904,14 +3938,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B26" s="193"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="200"/>
-      <c r="F26" s="201"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="121" t="s">
+    <row r="26" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="163"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="122" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="15">
@@ -3963,85 +3997,85 @@
         <v>30</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B27" s="193"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="200"/>
-      <c r="F27" s="201"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="121" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="163"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="79">
-        <v>0</v>
-      </c>
-      <c r="J27" s="79">
-        <v>0</v>
-      </c>
-      <c r="K27" s="79">
+      <c r="I27" s="78">
+        <v>0</v>
+      </c>
+      <c r="J27" s="78">
+        <v>0</v>
+      </c>
+      <c r="K27" s="78">
         <v>3</v>
       </c>
-      <c r="L27" s="99">
+      <c r="L27" s="98">
         <f>SUM(I27:K27)</f>
         <v>3</v>
       </c>
-      <c r="M27" s="79">
+      <c r="M27" s="78">
         <v>4</v>
       </c>
-      <c r="N27" s="79">
+      <c r="N27" s="78">
         <v>4</v>
       </c>
-      <c r="O27" s="83">
+      <c r="O27" s="82">
         <v>23</v>
       </c>
-      <c r="P27" s="98">
+      <c r="P27" s="97">
         <f>SUM(M27:O27)</f>
         <v>31</v>
       </c>
-      <c r="Q27" s="79">
+      <c r="Q27" s="78">
         <v>4</v>
       </c>
-      <c r="R27" s="79">
+      <c r="R27" s="78">
         <v>3</v>
       </c>
-      <c r="S27" s="79">
-        <v>5</v>
+      <c r="S27" s="78">
+        <v>7</v>
       </c>
       <c r="T27" s="56">
         <f>SUM(Q27:S27)</f>
-        <v>12</v>
-      </c>
-      <c r="U27" s="101"/>
-      <c r="V27" s="101"/>
-      <c r="W27" s="101"/>
+        <v>14</v>
+      </c>
+      <c r="U27" s="100"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="100"/>
       <c r="X27" s="56">
         <f>SUM(U27:W27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:25" ht="19.5" customHeight="1">
-      <c r="B28" s="193"/>
-      <c r="C28" s="125" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="168" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="170" t="s">
+    <row r="28" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="163"/>
+      <c r="C28" s="206" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="207" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="208" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="146">
+      <c r="F28" s="210">
         <v>0.82</v>
       </c>
-      <c r="G28" s="147">
+      <c r="G28" s="233">
         <f>R30</f>
         <v>0.85</v>
       </c>
-      <c r="H28" s="123" t="s">
+      <c r="H28" s="121" t="s">
         <v>26</v>
       </c>
       <c r="I28" s="24" t="s">
@@ -4096,14 +4130,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B29" s="193"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="169"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="146"/>
-      <c r="G29" s="147"/>
-      <c r="H29" s="123" t="s">
+    <row r="29" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="163"/>
+      <c r="C29" s="164"/>
+      <c r="D29" s="190"/>
+      <c r="E29" s="208"/>
+      <c r="F29" s="210"/>
+      <c r="G29" s="233"/>
+      <c r="H29" s="121" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="24">
@@ -4155,82 +4189,84 @@
         <v>0.85</v>
       </c>
       <c r="Y29" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B30" s="193"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="170"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="147"/>
-      <c r="H30" s="123" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="163"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="190"/>
+      <c r="E30" s="208"/>
+      <c r="F30" s="210"/>
+      <c r="G30" s="233"/>
+      <c r="H30" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="I30" s="77">
+      <c r="I30" s="76">
         <v>0.72</v>
       </c>
-      <c r="J30" s="76">
+      <c r="J30" s="75">
         <v>0.76</v>
       </c>
-      <c r="K30" s="76">
+      <c r="K30" s="75">
         <v>0.8</v>
       </c>
-      <c r="L30" s="87">
+      <c r="L30" s="86">
         <f>AVERAGE(I30:K30)</f>
         <v>0.76000000000000012</v>
       </c>
-      <c r="M30" s="77">
+      <c r="M30" s="76">
         <v>0.75</v>
       </c>
-      <c r="N30" s="76">
+      <c r="N30" s="75">
         <v>0.84</v>
       </c>
-      <c r="O30" s="77">
+      <c r="O30" s="76">
         <v>0.73</v>
       </c>
-      <c r="P30" s="94">
+      <c r="P30" s="93">
         <f>AVERAGE(M30:O30)</f>
         <v>0.77333333333333332</v>
       </c>
-      <c r="Q30" s="76">
+      <c r="Q30" s="75">
         <v>0.82</v>
       </c>
-      <c r="R30" s="76">
+      <c r="R30" s="75">
         <v>0.85</v>
       </c>
-      <c r="S30" s="64"/>
-      <c r="T30" s="65">
+      <c r="S30" s="75">
+        <v>0.82</v>
+      </c>
+      <c r="T30" s="64">
         <f>AVERAGE(Q30:S30)</f>
-        <v>0.83499999999999996</v>
-      </c>
-      <c r="U30" s="64"/>
-      <c r="V30" s="64"/>
+        <v>0.83</v>
+      </c>
+      <c r="U30" s="63"/>
+      <c r="V30" s="63"/>
       <c r="W30" s="19"/>
-      <c r="X30" s="65" t="e">
+      <c r="X30" s="64" t="e">
         <f>AVERAGE(U30:W30)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="2:25" ht="19.5" customHeight="1">
-      <c r="B31" s="193"/>
-      <c r="C31" s="127" t="s">
+    <row r="31" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="163"/>
+      <c r="C31" s="144" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="128" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="179">
+      <c r="E31" s="156">
         <v>0.82</v>
       </c>
-      <c r="F31" s="143">
+      <c r="F31" s="201">
         <v>0.7</v>
       </c>
-      <c r="G31" s="179">
+      <c r="G31" s="156">
         <v>0.83</v>
       </c>
-      <c r="H31" s="121" t="s">
+      <c r="H31" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I31" s="26" t="s">
@@ -4282,14 +4318,14 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="32" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B32" s="193"/>
-      <c r="C32" s="127"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="143"/>
-      <c r="G32" s="179"/>
-      <c r="H32" s="121" t="s">
+    <row r="32" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="163"/>
+      <c r="C32" s="144"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="201"/>
+      <c r="G32" s="156"/>
+      <c r="H32" s="122" t="s">
         <v>27</v>
       </c>
       <c r="I32" s="26">
@@ -4341,76 +4377,80 @@
         <v>0.7</v>
       </c>
       <c r="Y32" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="163"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="171"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="201"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="122" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="26" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B33" s="193"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="179"/>
-      <c r="F33" s="143"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="121" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>50</v>
-      </c>
       <c r="J33" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33" s="76">
+        <v>49</v>
+      </c>
+      <c r="K33" s="75">
         <v>0.83</v>
       </c>
-      <c r="L33" s="87">
+      <c r="L33" s="86">
         <v>0.83</v>
       </c>
       <c r="M33" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="O33" s="76">
+        <v>49</v>
+      </c>
+      <c r="O33" s="75">
         <v>0.81</v>
       </c>
-      <c r="P33" s="87">
+      <c r="P33" s="86">
         <v>0.81</v>
       </c>
       <c r="Q33" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R33" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="S33" s="49"/>
-      <c r="T33" s="62"/>
+        <v>49</v>
+      </c>
+      <c r="S33" s="86">
+        <v>0.82</v>
+      </c>
+      <c r="T33" s="86">
+        <v>0.82</v>
+      </c>
       <c r="U33" s="49"/>
       <c r="V33" s="49"/>
       <c r="W33" s="15"/>
       <c r="X33" s="33"/>
     </row>
-    <row r="34" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B34" s="185" t="s">
+    <row r="34" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="148" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="164" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="126" t="s">
+      <c r="D34" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="148" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="152">
+      <c r="E34" s="199">
         <v>0.77</v>
       </c>
-      <c r="F34" s="146">
+      <c r="F34" s="210">
         <v>0.85</v>
       </c>
-      <c r="G34" s="156">
+      <c r="G34" s="197">
         <v>0.79</v>
       </c>
-      <c r="H34" s="123" t="s">
+      <c r="H34" s="121" t="s">
         <v>26</v>
       </c>
       <c r="I34" s="21">
@@ -4462,14 +4502,14 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="35" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B35" s="186"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="148"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="146"/>
-      <c r="G35" s="156"/>
-      <c r="H35" s="123" t="s">
+    <row r="35" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="149"/>
+      <c r="C35" s="164"/>
+      <c r="D35" s="154"/>
+      <c r="E35" s="199"/>
+      <c r="F35" s="210"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="121" t="s">
         <v>27</v>
       </c>
       <c r="I35" s="21">
@@ -4521,68 +4561,72 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="36" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B36" s="186"/>
-      <c r="C36" s="194"/>
-      <c r="D36" s="190"/>
-      <c r="E36" s="153"/>
-      <c r="F36" s="146"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="123" t="s">
+    <row r="36" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="149"/>
+      <c r="C36" s="165"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="200"/>
+      <c r="F36" s="210"/>
+      <c r="G36" s="198"/>
+      <c r="H36" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="I36" s="76">
+      <c r="I36" s="75">
         <v>0.78</v>
       </c>
-      <c r="J36" s="82">
+      <c r="J36" s="81">
         <v>0.77</v>
       </c>
-      <c r="K36" s="76">
+      <c r="K36" s="75">
         <v>0.79</v>
       </c>
-      <c r="L36" s="87">
+      <c r="L36" s="86">
         <v>0.79</v>
       </c>
-      <c r="M36" s="76">
+      <c r="M36" s="75">
         <v>0.8</v>
       </c>
-      <c r="N36" s="77">
+      <c r="N36" s="76">
         <v>0.8</v>
       </c>
-      <c r="O36" s="82">
+      <c r="O36" s="81">
         <v>0.79600000000000004</v>
       </c>
-      <c r="P36" s="94">
+      <c r="P36" s="93">
         <v>0.8</v>
       </c>
-      <c r="Q36" s="77">
+      <c r="Q36" s="76">
         <v>0.79</v>
       </c>
-      <c r="R36" s="82">
+      <c r="R36" s="81">
         <v>0.8</v>
       </c>
-      <c r="S36" s="50"/>
-      <c r="T36" s="66"/>
+      <c r="S36" s="81">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="T36" s="125">
+        <v>0.76</v>
+      </c>
       <c r="U36" s="50"/>
       <c r="V36" s="50"/>
       <c r="W36" s="50"/>
-      <c r="X36" s="66"/>
-    </row>
-    <row r="37" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B37" s="186"/>
-      <c r="C37" s="136" t="s">
+      <c r="X36" s="65"/>
+    </row>
+    <row r="37" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="149"/>
+      <c r="C37" s="224" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="227" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="139" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="159" t="s">
+      <c r="E37" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="160">
-        <v>0.9</v>
-      </c>
-      <c r="G37" s="163">
+      <c r="F37" s="215">
+        <v>0.9</v>
+      </c>
+      <c r="G37" s="218">
         <v>0.6</v>
       </c>
       <c r="H37" s="39" t="s">
@@ -4640,13 +4684,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B38" s="186"/>
-      <c r="C38" s="137"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="160"/>
-      <c r="G38" s="163"/>
+    <row r="38" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="149"/>
+      <c r="C38" s="225"/>
+      <c r="D38" s="228"/>
+      <c r="E38" s="214"/>
+      <c r="F38" s="215"/>
+      <c r="G38" s="218"/>
       <c r="H38" s="39" t="s">
         <v>27</v>
       </c>
@@ -4699,132 +4743,136 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="39" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B39" s="186"/>
-      <c r="C39" s="138"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="159"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="163"/>
+    <row r="39" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="149"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="214"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="218"/>
       <c r="H39" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="I39" s="77">
+      <c r="I39" s="76">
         <v>0.44</v>
       </c>
-      <c r="J39" s="77">
+      <c r="J39" s="76">
         <v>0.44</v>
       </c>
-      <c r="K39" s="76">
+      <c r="K39" s="75">
         <v>0.91</v>
       </c>
-      <c r="L39" s="94">
+      <c r="L39" s="93">
         <v>0.6</v>
       </c>
-      <c r="M39" s="77">
-        <v>0</v>
-      </c>
-      <c r="N39" s="77">
+      <c r="M39" s="76">
+        <v>0</v>
+      </c>
+      <c r="N39" s="76">
         <v>0.6</v>
       </c>
-      <c r="O39" s="77">
+      <c r="O39" s="76">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P39" s="94">
+      <c r="P39" s="93">
         <v>0.4</v>
       </c>
-      <c r="Q39" s="77">
+      <c r="Q39" s="76">
         <v>0.2</v>
       </c>
-      <c r="R39" s="82">
+      <c r="R39" s="81">
         <v>0.7</v>
       </c>
-      <c r="S39" s="59"/>
-      <c r="T39" s="59"/>
+      <c r="S39" s="81">
+        <v>0.77</v>
+      </c>
+      <c r="T39" s="99">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="U39" s="59"/>
       <c r="V39" s="59"/>
       <c r="W39" s="59"/>
       <c r="X39" s="18"/>
     </row>
-    <row r="40" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B40" s="186"/>
-      <c r="C40" s="204" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="207" t="s">
+    <row r="40" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="149"/>
+      <c r="C40" s="176" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="208" t="s">
+      <c r="D40" s="179" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="180" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="146">
-        <v>0.9</v>
-      </c>
-      <c r="G40" s="157">
+      <c r="F40" s="210">
+        <v>0.9</v>
+      </c>
+      <c r="G40" s="212">
         <v>0.85</v>
       </c>
       <c r="H40" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="M40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="N40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="O40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="P40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="R40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="S40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="T40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="U40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="V40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="W40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="X40" s="67" t="s">
+      <c r="I40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="O40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="S40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="T40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="U40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="V40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="W40" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="X40" s="66" t="s">
         <v>32</v>
       </c>
       <c r="Y40" s="54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B41" s="186"/>
-      <c r="C41" s="205"/>
-      <c r="D41" s="148"/>
-      <c r="E41" s="208"/>
-      <c r="F41" s="146"/>
-      <c r="G41" s="158"/>
+    <row r="41" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="149"/>
+      <c r="C41" s="177"/>
+      <c r="D41" s="154"/>
+      <c r="E41" s="180"/>
+      <c r="F41" s="210"/>
+      <c r="G41" s="213"/>
       <c r="H41" s="58" t="s">
         <v>27</v>
       </c>
@@ -4877,68 +4925,72 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="42" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B42" s="186"/>
-      <c r="C42" s="206"/>
-      <c r="D42" s="148"/>
-      <c r="E42" s="208"/>
-      <c r="F42" s="146"/>
-      <c r="G42" s="158"/>
+    <row r="42" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="149"/>
+      <c r="C42" s="178"/>
+      <c r="D42" s="154"/>
+      <c r="E42" s="180"/>
+      <c r="F42" s="210"/>
+      <c r="G42" s="213"/>
       <c r="H42" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="I42" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="K42" s="82">
+      <c r="I42" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="81">
         <v>0.85</v>
       </c>
-      <c r="L42" s="100">
+      <c r="L42" s="99">
         <v>0.85</v>
       </c>
-      <c r="M42" s="76">
+      <c r="M42" s="75">
         <v>1</v>
       </c>
-      <c r="N42" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="O42" s="82">
+      <c r="N42" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="O42" s="81">
         <v>0.15</v>
       </c>
-      <c r="P42" s="100">
+      <c r="P42" s="99">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Q42" s="82">
+      <c r="Q42" s="81">
         <v>0.7</v>
       </c>
-      <c r="R42" s="76">
+      <c r="R42" s="75">
         <v>1</v>
       </c>
-      <c r="S42" s="51"/>
-      <c r="T42" s="51"/>
+      <c r="S42" s="75">
+        <v>0.92</v>
+      </c>
+      <c r="T42" s="99">
+        <v>0.87</v>
+      </c>
       <c r="U42" s="51"/>
       <c r="V42" s="51"/>
       <c r="W42" s="51"/>
       <c r="X42" s="13"/>
     </row>
-    <row r="43" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B43" s="186"/>
-      <c r="C43" s="144" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="139" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="159" t="s">
+    <row r="43" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="149"/>
+      <c r="C43" s="231" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="227" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="F43" s="160">
+      <c r="F43" s="215">
         <v>1</v>
       </c>
-      <c r="G43" s="162">
+      <c r="G43" s="217">
         <v>0.93</v>
       </c>
       <c r="H43" s="39" t="s">
@@ -4996,13 +5048,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B44" s="186"/>
-      <c r="C44" s="145"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="159"/>
-      <c r="F44" s="160"/>
-      <c r="G44" s="162"/>
+    <row r="44" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="149"/>
+      <c r="C44" s="232"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="214"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="217"/>
       <c r="H44" s="39" t="s">
         <v>27</v>
       </c>
@@ -5055,252 +5107,260 @@
         <v>1</v>
       </c>
       <c r="Y44" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B45" s="186"/>
-      <c r="C45" s="145"/>
-      <c r="D45" s="140"/>
-      <c r="E45" s="159"/>
-      <c r="F45" s="161"/>
-      <c r="G45" s="162"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="149"/>
+      <c r="C45" s="232"/>
+      <c r="D45" s="228"/>
+      <c r="E45" s="214"/>
+      <c r="F45" s="216"/>
+      <c r="G45" s="217"/>
       <c r="H45" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="K45" s="82">
+      <c r="I45" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="81">
         <v>0.93</v>
       </c>
-      <c r="L45" s="100">
+      <c r="L45" s="99">
         <v>0.93</v>
       </c>
-      <c r="M45" s="76">
+      <c r="M45" s="75">
         <v>1</v>
       </c>
-      <c r="N45" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="O45" s="82">
+      <c r="N45" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" s="81">
         <v>0.98</v>
       </c>
-      <c r="P45" s="100">
+      <c r="P45" s="99">
         <v>0.99</v>
       </c>
-      <c r="Q45" s="82">
+      <c r="Q45" s="81">
         <v>0.95</v>
       </c>
-      <c r="R45" s="76">
+      <c r="R45" s="75">
         <v>1</v>
       </c>
-      <c r="S45" s="59"/>
-      <c r="T45" s="59"/>
+      <c r="S45" s="75">
+        <v>1</v>
+      </c>
+      <c r="T45" s="99">
+        <v>0.98</v>
+      </c>
       <c r="U45" s="59"/>
       <c r="V45" s="59"/>
       <c r="W45" s="59"/>
       <c r="X45" s="18"/>
     </row>
-    <row r="46" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B46" s="186"/>
-      <c r="C46" s="126" t="s">
+    <row r="46" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="149"/>
+      <c r="C46" s="164" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="234">
+        <v>372</v>
+      </c>
+      <c r="F46" s="235">
+        <v>366</v>
+      </c>
+      <c r="G46" s="202">
+        <v>365</v>
+      </c>
+      <c r="H46" s="121" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" s="104">
+        <v>383</v>
+      </c>
+      <c r="J46" s="104">
+        <v>381</v>
+      </c>
+      <c r="K46" s="104">
+        <v>380</v>
+      </c>
+      <c r="L46" s="105">
+        <v>381</v>
+      </c>
+      <c r="M46" s="104">
+        <v>378</v>
+      </c>
+      <c r="N46" s="104">
+        <v>376</v>
+      </c>
+      <c r="O46" s="104">
+        <v>374</v>
+      </c>
+      <c r="P46" s="105">
+        <v>376</v>
+      </c>
+      <c r="Q46" s="104">
+        <v>372</v>
+      </c>
+      <c r="R46" s="104">
+        <v>370</v>
+      </c>
+      <c r="S46" s="104">
+        <v>371</v>
+      </c>
+      <c r="T46" s="105">
+        <v>371</v>
+      </c>
+      <c r="U46" s="104">
+        <v>372</v>
+      </c>
+      <c r="V46" s="104">
+        <v>371</v>
+      </c>
+      <c r="W46" s="104">
+        <v>371</v>
+      </c>
+      <c r="X46" s="105">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="149"/>
+      <c r="C47" s="164"/>
+      <c r="D47" s="154"/>
+      <c r="E47" s="234"/>
+      <c r="F47" s="235"/>
+      <c r="G47" s="202"/>
+      <c r="H47" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="104">
+        <v>366</v>
+      </c>
+      <c r="J47" s="104">
+        <v>366</v>
+      </c>
+      <c r="K47" s="104">
+        <v>366</v>
+      </c>
+      <c r="L47" s="105">
+        <v>366</v>
+      </c>
+      <c r="M47" s="104">
+        <v>366</v>
+      </c>
+      <c r="N47" s="104">
+        <v>366</v>
+      </c>
+      <c r="O47" s="104">
+        <v>366</v>
+      </c>
+      <c r="P47" s="105">
+        <v>366</v>
+      </c>
+      <c r="Q47" s="104">
+        <v>366</v>
+      </c>
+      <c r="R47" s="104">
+        <v>366</v>
+      </c>
+      <c r="S47" s="104">
+        <v>366</v>
+      </c>
+      <c r="T47" s="105">
+        <v>366</v>
+      </c>
+      <c r="U47" s="104">
+        <v>366</v>
+      </c>
+      <c r="V47" s="104">
+        <v>366</v>
+      </c>
+      <c r="W47" s="104">
+        <v>366</v>
+      </c>
+      <c r="X47" s="105">
+        <v>366</v>
+      </c>
+      <c r="Y47" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="148" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="149">
-        <v>372</v>
-      </c>
-      <c r="F46" s="150">
-        <v>366</v>
-      </c>
-      <c r="G46" s="135">
+    </row>
+    <row r="48" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="149"/>
+      <c r="C48" s="164"/>
+      <c r="D48" s="154"/>
+      <c r="E48" s="234"/>
+      <c r="F48" s="235"/>
+      <c r="G48" s="202"/>
+      <c r="H48" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" s="74">
+        <v>379</v>
+      </c>
+      <c r="J48" s="74">
+        <v>373</v>
+      </c>
+      <c r="K48" s="74">
+        <v>380</v>
+      </c>
+      <c r="L48" s="94">
+        <v>377</v>
+      </c>
+      <c r="M48" s="74">
+        <v>377</v>
+      </c>
+      <c r="N48" s="85">
         <v>365</v>
       </c>
-      <c r="H46" s="123" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46" s="105">
-        <v>383</v>
-      </c>
-      <c r="J46" s="105">
-        <v>381</v>
-      </c>
-      <c r="K46" s="105">
-        <v>380</v>
-      </c>
-      <c r="L46" s="106">
-        <v>381</v>
-      </c>
-      <c r="M46" s="105">
-        <v>378</v>
-      </c>
-      <c r="N46" s="105">
-        <v>376</v>
-      </c>
-      <c r="O46" s="105">
-        <v>374</v>
-      </c>
-      <c r="P46" s="106">
-        <v>376</v>
-      </c>
-      <c r="Q46" s="105">
-        <v>372</v>
-      </c>
-      <c r="R46" s="105">
-        <v>370</v>
-      </c>
-      <c r="S46" s="105">
-        <v>371</v>
-      </c>
-      <c r="T46" s="106">
-        <v>371</v>
-      </c>
-      <c r="U46" s="105">
-        <v>372</v>
-      </c>
-      <c r="V46" s="105">
-        <v>371</v>
-      </c>
-      <c r="W46" s="105">
-        <v>371</v>
-      </c>
-      <c r="X46" s="106">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B47" s="186"/>
-      <c r="C47" s="126"/>
-      <c r="D47" s="148"/>
-      <c r="E47" s="149"/>
-      <c r="F47" s="150"/>
-      <c r="G47" s="135"/>
-      <c r="H47" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="I47" s="105">
-        <v>366</v>
-      </c>
-      <c r="J47" s="105">
-        <v>366</v>
-      </c>
-      <c r="K47" s="105">
-        <v>366</v>
-      </c>
-      <c r="L47" s="106">
-        <v>366</v>
-      </c>
-      <c r="M47" s="105">
-        <v>366</v>
-      </c>
-      <c r="N47" s="105">
-        <v>366</v>
-      </c>
-      <c r="O47" s="105">
-        <v>366</v>
-      </c>
-      <c r="P47" s="106">
-        <v>366</v>
-      </c>
-      <c r="Q47" s="105">
-        <v>366</v>
-      </c>
-      <c r="R47" s="105">
-        <v>366</v>
-      </c>
-      <c r="S47" s="105">
-        <v>366</v>
-      </c>
-      <c r="T47" s="106">
-        <v>366</v>
-      </c>
-      <c r="U47" s="105">
-        <v>366</v>
-      </c>
-      <c r="V47" s="105">
-        <v>366</v>
-      </c>
-      <c r="W47" s="105">
-        <v>366</v>
-      </c>
-      <c r="X47" s="106">
-        <v>366</v>
-      </c>
-      <c r="Y47" s="7" t="s">
+      <c r="O48" s="85">
+        <v>365</v>
+      </c>
+      <c r="P48" s="94">
+        <v>369</v>
+      </c>
+      <c r="Q48" s="85">
+        <v>363</v>
+      </c>
+      <c r="R48" s="85">
+        <v>360</v>
+      </c>
+      <c r="S48" s="85">
+        <v>363</v>
+      </c>
+      <c r="T48" s="96">
+        <v>362</v>
+      </c>
+      <c r="U48" s="104"/>
+      <c r="V48" s="104"/>
+      <c r="W48" s="104"/>
+      <c r="X48" s="105"/>
+    </row>
+    <row r="49" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="149"/>
+      <c r="C49" s="185" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B48" s="186"/>
-      <c r="C48" s="126"/>
-      <c r="D48" s="148"/>
-      <c r="E48" s="149"/>
-      <c r="F48" s="150"/>
-      <c r="G48" s="135"/>
-      <c r="H48" s="123" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" s="75">
-        <v>379</v>
-      </c>
-      <c r="J48" s="75">
-        <v>373</v>
-      </c>
-      <c r="K48" s="75">
-        <v>380</v>
-      </c>
-      <c r="L48" s="95">
-        <v>377</v>
-      </c>
-      <c r="M48" s="75">
-        <v>377</v>
-      </c>
-      <c r="N48" s="86">
-        <v>365</v>
-      </c>
-      <c r="O48" s="86">
-        <v>365</v>
-      </c>
-      <c r="P48" s="95">
-        <v>369</v>
-      </c>
-      <c r="Q48" s="86">
-        <v>363</v>
-      </c>
-      <c r="R48" s="86">
-        <v>360</v>
-      </c>
-      <c r="S48" s="105"/>
-      <c r="T48" s="106"/>
-      <c r="U48" s="105"/>
-      <c r="V48" s="105"/>
-      <c r="W48" s="105"/>
-      <c r="X48" s="106"/>
-    </row>
-    <row r="49" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B49" s="186"/>
-      <c r="C49" s="174" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" s="175" t="s">
-        <v>48</v>
-      </c>
-      <c r="E49" s="177">
+      <c r="D49" s="186" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="187">
         <v>0.71</v>
       </c>
-      <c r="F49" s="196">
+      <c r="F49" s="167">
         <v>0.92</v>
       </c>
-      <c r="G49" s="131">
+      <c r="G49" s="221">
         <v>0.72</v>
       </c>
-      <c r="H49" s="121" t="s">
+      <c r="H49" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I49" s="26">
@@ -5352,14 +5412,14 @@
         <v>0.85814814814814822</v>
       </c>
     </row>
-    <row r="50" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B50" s="186"/>
-      <c r="C50" s="127"/>
-      <c r="D50" s="176"/>
-      <c r="E50" s="177"/>
-      <c r="F50" s="196"/>
-      <c r="G50" s="132"/>
-      <c r="H50" s="121" t="s">
+    <row r="50" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="149"/>
+      <c r="C50" s="144"/>
+      <c r="D50" s="145"/>
+      <c r="E50" s="187"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="222"/>
+      <c r="H50" s="122" t="s">
         <v>27</v>
       </c>
       <c r="I50" s="26">
@@ -5411,71 +5471,75 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="51" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B51" s="186"/>
-      <c r="C51" s="127"/>
-      <c r="D51" s="176"/>
-      <c r="E51" s="177"/>
-      <c r="F51" s="196"/>
-      <c r="G51" s="132"/>
-      <c r="H51" s="121" t="s">
+    <row r="51" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="149"/>
+      <c r="C51" s="144"/>
+      <c r="D51" s="145"/>
+      <c r="E51" s="187"/>
+      <c r="F51" s="167"/>
+      <c r="G51" s="222"/>
+      <c r="H51" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="I51" s="77">
+      <c r="I51" s="76">
         <v>0.83</v>
       </c>
-      <c r="J51" s="77">
+      <c r="J51" s="76">
         <v>0.6</v>
       </c>
-      <c r="K51" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="L51" s="94">
+      <c r="K51" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="93">
         <v>0.72</v>
       </c>
-      <c r="M51" s="77">
+      <c r="M51" s="76">
         <v>0.85</v>
       </c>
-      <c r="N51" s="77">
+      <c r="N51" s="76">
         <v>0.89</v>
       </c>
-      <c r="O51" s="77">
+      <c r="O51" s="76">
         <v>0.91</v>
       </c>
-      <c r="P51" s="94">
+      <c r="P51" s="93">
         <v>0.82</v>
       </c>
-      <c r="Q51" s="77">
+      <c r="Q51" s="76">
         <v>0.89</v>
       </c>
-      <c r="R51" s="77">
+      <c r="R51" s="76">
         <v>0.89</v>
       </c>
-      <c r="S51" s="49"/>
-      <c r="T51" s="48"/>
+      <c r="S51" s="76">
+        <v>0.88</v>
+      </c>
+      <c r="T51" s="76">
+        <v>0.88</v>
+      </c>
       <c r="U51" s="47"/>
       <c r="V51" s="47"/>
       <c r="W51" s="26"/>
       <c r="X51" s="27"/>
     </row>
-    <row r="52" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B52" s="186"/>
-      <c r="C52" s="126" t="s">
+    <row r="52" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="149"/>
+      <c r="C52" s="164" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="154" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" s="168" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" s="211" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="148" t="s">
-        <v>48</v>
-      </c>
-      <c r="E52" s="197" t="s">
-        <v>35</v>
-      </c>
-      <c r="F52" s="154" t="s">
-        <v>64</v>
-      </c>
-      <c r="G52" s="156">
+      <c r="G52" s="197">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H52" s="123" t="s">
+      <c r="H52" s="121" t="s">
         <v>26</v>
       </c>
       <c r="I52" s="24" t="s">
@@ -5530,64 +5594,64 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B53" s="186"/>
-      <c r="C53" s="126"/>
-      <c r="D53" s="148"/>
-      <c r="E53" s="197"/>
-      <c r="F53" s="155"/>
-      <c r="G53" s="156"/>
-      <c r="H53" s="123" t="s">
+    <row r="53" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="149"/>
+      <c r="C53" s="164"/>
+      <c r="D53" s="154"/>
+      <c r="E53" s="168"/>
+      <c r="F53" s="194"/>
+      <c r="G53" s="197"/>
+      <c r="H53" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="I53" s="133"/>
-      <c r="J53" s="133"/>
-      <c r="K53" s="133"/>
-      <c r="L53" s="107" t="s">
+      <c r="I53" s="131"/>
+      <c r="J53" s="131"/>
+      <c r="K53" s="131"/>
+      <c r="L53" s="106" t="s">
+        <v>63</v>
+      </c>
+      <c r="M53" s="131"/>
+      <c r="N53" s="131"/>
+      <c r="O53" s="131"/>
+      <c r="P53" s="106" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q53" s="131"/>
+      <c r="R53" s="131"/>
+      <c r="S53" s="131"/>
+      <c r="T53" s="106" t="s">
+        <v>63</v>
+      </c>
+      <c r="U53" s="131"/>
+      <c r="V53" s="131"/>
+      <c r="W53" s="131"/>
+      <c r="X53" s="106" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y53" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="M53" s="133"/>
-      <c r="N53" s="133"/>
-      <c r="O53" s="133"/>
-      <c r="P53" s="107" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q53" s="133"/>
-      <c r="R53" s="133"/>
-      <c r="S53" s="133"/>
-      <c r="T53" s="107" t="s">
-        <v>64</v>
-      </c>
-      <c r="U53" s="133"/>
-      <c r="V53" s="133"/>
-      <c r="W53" s="133"/>
-      <c r="X53" s="107" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y53" s="7" t="s">
+    </row>
+    <row r="54" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="149"/>
+      <c r="C54" s="164"/>
+      <c r="D54" s="154"/>
+      <c r="E54" s="168"/>
+      <c r="F54" s="194"/>
+      <c r="G54" s="197"/>
+      <c r="H54" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="24" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="54" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B54" s="186"/>
-      <c r="C54" s="126"/>
-      <c r="D54" s="148"/>
-      <c r="E54" s="197"/>
-      <c r="F54" s="155"/>
-      <c r="G54" s="156"/>
-      <c r="H54" s="123" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="24" t="s">
+      <c r="J54" s="24" t="s">
         <v>66</v>
-      </c>
-      <c r="J54" s="24" t="s">
-        <v>67</v>
       </c>
       <c r="K54" s="24">
         <v>0.28799999999999998</v>
       </c>
-      <c r="L54" s="94">
+      <c r="L54" s="93">
         <v>0.28999999999999998</v>
       </c>
       <c r="M54" s="24">
@@ -5599,7 +5663,7 @@
       <c r="O54" s="24">
         <v>0.13</v>
       </c>
-      <c r="P54" s="94">
+      <c r="P54" s="93">
         <v>0.16</v>
       </c>
       <c r="Q54" s="24">
@@ -5608,33 +5672,37 @@
       <c r="R54" s="24">
         <v>0.214</v>
       </c>
-      <c r="S54" s="24"/>
-      <c r="T54" s="25"/>
+      <c r="S54" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="T54" s="93">
+        <v>0.24</v>
+      </c>
       <c r="U54" s="24"/>
       <c r="V54" s="24"/>
       <c r="W54" s="24"/>
       <c r="X54" s="25"/>
     </row>
-    <row r="55" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B55" s="186"/>
-      <c r="C55" s="127" t="s">
+    <row r="55" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="149"/>
+      <c r="C55" s="144" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="176" t="s">
-        <v>69</v>
-      </c>
-      <c r="E55" s="212">
+      <c r="E55" s="146">
         <f>X55</f>
         <v>40</v>
       </c>
-      <c r="F55" s="195">
+      <c r="F55" s="166">
         <v>55</v>
       </c>
-      <c r="G55" s="134">
+      <c r="G55" s="223">
         <f>X57</f>
-        <v>47</v>
-      </c>
-      <c r="H55" s="121" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" s="122" t="s">
         <v>26</v>
       </c>
       <c r="I55" s="15">
@@ -5686,122 +5754,123 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B56" s="186"/>
-      <c r="C56" s="127"/>
-      <c r="D56" s="176"/>
-      <c r="E56" s="212"/>
-      <c r="F56" s="195"/>
-      <c r="G56" s="134"/>
-      <c r="H56" s="121" t="s">
+    <row r="56" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="149"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="145"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="166"/>
+      <c r="G56" s="223"/>
+      <c r="H56" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="151" t="s">
-        <v>32</v>
-      </c>
-      <c r="J56" s="151"/>
-      <c r="K56" s="151"/>
+      <c r="I56" s="209" t="s">
+        <v>32</v>
+      </c>
+      <c r="J56" s="209"/>
+      <c r="K56" s="209"/>
       <c r="L56" s="18">
         <v>13</v>
       </c>
-      <c r="M56" s="151" t="s">
-        <v>32</v>
-      </c>
-      <c r="N56" s="151"/>
-      <c r="O56" s="151"/>
+      <c r="M56" s="209" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56" s="209"/>
+      <c r="O56" s="209"/>
       <c r="P56" s="18">
         <v>27</v>
       </c>
-      <c r="Q56" s="151" t="s">
-        <v>32</v>
-      </c>
-      <c r="R56" s="151"/>
-      <c r="S56" s="151"/>
+      <c r="Q56" s="209" t="s">
+        <v>32</v>
+      </c>
+      <c r="R56" s="209"/>
+      <c r="S56" s="209"/>
       <c r="T56" s="18">
         <v>41</v>
       </c>
-      <c r="U56" s="151" t="s">
-        <v>32</v>
-      </c>
-      <c r="V56" s="151"/>
-      <c r="W56" s="151"/>
+      <c r="U56" s="209" t="s">
+        <v>32</v>
+      </c>
+      <c r="V56" s="209"/>
+      <c r="W56" s="209"/>
       <c r="X56" s="18">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B57" s="186"/>
-      <c r="C57" s="127"/>
-      <c r="D57" s="176"/>
-      <c r="E57" s="212"/>
-      <c r="F57" s="195"/>
-      <c r="G57" s="134"/>
-      <c r="H57" s="121" t="s">
+    <row r="57" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="149"/>
+      <c r="C57" s="144"/>
+      <c r="D57" s="145"/>
+      <c r="E57" s="146"/>
+      <c r="F57" s="166"/>
+      <c r="G57" s="223"/>
+      <c r="H57" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="I57" s="108">
-        <v>0</v>
-      </c>
-      <c r="J57" s="108">
-        <v>0</v>
-      </c>
-      <c r="K57" s="108">
+      <c r="I57" s="107">
+        <v>0</v>
+      </c>
+      <c r="J57" s="107">
+        <v>0</v>
+      </c>
+      <c r="K57" s="107">
         <v>17</v>
       </c>
-      <c r="L57" s="89">
+      <c r="L57" s="88">
         <v>17</v>
       </c>
-      <c r="M57" s="108">
+      <c r="M57" s="107">
         <v>25</v>
       </c>
-      <c r="N57" s="108">
-        <v>0</v>
-      </c>
-      <c r="O57" s="108">
-        <v>0</v>
-      </c>
-      <c r="P57" s="113">
+      <c r="N57" s="107">
+        <v>0</v>
+      </c>
+      <c r="O57" s="107">
+        <v>0</v>
+      </c>
+      <c r="P57" s="112">
         <v>42</v>
       </c>
-      <c r="Q57" s="108">
+      <c r="Q57" s="107">
         <v>2</v>
       </c>
-      <c r="R57" s="108">
+      <c r="R57" s="107">
         <v>3</v>
       </c>
-      <c r="S57" s="108"/>
-      <c r="T57" s="109">
-        <f>SUM(P57:S57)</f>
-        <v>47</v>
-      </c>
-      <c r="U57" s="108"/>
-      <c r="V57" s="108"/>
-      <c r="W57" s="108"/>
-      <c r="X57" s="109">
+      <c r="S57" s="107">
+        <v>4</v>
+      </c>
+      <c r="T57" s="112">
+        <v>51</v>
+      </c>
+      <c r="U57" s="107"/>
+      <c r="V57" s="107"/>
+      <c r="W57" s="107"/>
+      <c r="X57" s="108">
         <f>SUM(T57:W57)</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="58" spans="2:25" ht="15" hidden="1" customHeight="1">
-      <c r="B58" s="185" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="2:25" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="148" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="157" t="s">
         <v>70</v>
       </c>
-      <c r="C58" s="187" t="s">
+      <c r="D58" s="160" t="s">
         <v>71</v>
       </c>
-      <c r="D58" s="190" t="s">
-        <v>72</v>
-      </c>
-      <c r="E58" s="219">
+      <c r="E58" s="136">
         <v>92.5</v>
       </c>
-      <c r="F58" s="228">
+      <c r="F58" s="133">
         <v>93</v>
       </c>
-      <c r="G58" s="219">
+      <c r="G58" s="136">
         <v>92.5</v>
       </c>
-      <c r="H58" s="123" t="s">
+      <c r="H58" s="121" t="s">
         <v>26</v>
       </c>
       <c r="I58" s="34">
@@ -5853,17 +5922,17 @@
         <v>92.5</v>
       </c>
       <c r="Y58" s="37" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" spans="2:25" ht="15" hidden="1" customHeight="1">
-      <c r="B59" s="186"/>
-      <c r="C59" s="188"/>
-      <c r="D59" s="191"/>
-      <c r="E59" s="220"/>
-      <c r="F59" s="229"/>
-      <c r="G59" s="220"/>
-      <c r="H59" s="123" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="2:25" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="149"/>
+      <c r="C59" s="158"/>
+      <c r="D59" s="161"/>
+      <c r="E59" s="137"/>
+      <c r="F59" s="134"/>
+      <c r="G59" s="137"/>
+      <c r="H59" s="121" t="s">
         <v>27</v>
       </c>
       <c r="I59" s="19">
@@ -5915,17 +5984,17 @@
         <v>93</v>
       </c>
       <c r="Y59" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="2:25" ht="15" hidden="1" customHeight="1">
-      <c r="B60" s="186"/>
-      <c r="C60" s="189"/>
-      <c r="D60" s="192"/>
-      <c r="E60" s="221"/>
-      <c r="F60" s="230"/>
-      <c r="G60" s="221"/>
-      <c r="H60" s="123" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="2:25" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="149"/>
+      <c r="C60" s="159"/>
+      <c r="D60" s="162"/>
+      <c r="E60" s="138"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="138"/>
+      <c r="H60" s="121" t="s">
         <v>28</v>
       </c>
       <c r="I60" s="36">
@@ -5943,583 +6012,585 @@
       <c r="S60" s="22"/>
       <c r="T60" s="20"/>
       <c r="U60" s="22"/>
-      <c r="V60" s="102"/>
-      <c r="W60" s="102"/>
+      <c r="V60" s="101"/>
+      <c r="W60" s="101"/>
       <c r="X60" s="20"/>
     </row>
-    <row r="61" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B61" s="185" t="s">
+    <row r="61" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="148" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="C61" s="213" t="s">
-        <v>76</v>
-      </c>
-      <c r="D61" s="148" t="s">
+      <c r="D61" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="E61" s="218">
+      <c r="E61" s="155">
         <f>L61+P61+T61+X61</f>
         <v>30.187825999999998</v>
       </c>
-      <c r="F61" s="232">
+      <c r="F61" s="140">
         <f>SUM(L62,P62,T62,X62)</f>
         <v>28</v>
       </c>
-      <c r="G61" s="227">
+      <c r="G61" s="132">
         <f>L63+P63+T63+X63</f>
-        <v>16.622583999999996</v>
-      </c>
-      <c r="H61" s="123" t="s">
+        <v>18.672584000000001</v>
+      </c>
+      <c r="H61" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="69">
+      <c r="I61" s="68">
         <v>1.7</v>
       </c>
-      <c r="J61" s="69">
+      <c r="J61" s="68">
         <v>2.5150000000000001</v>
       </c>
-      <c r="K61" s="69">
+      <c r="K61" s="68">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L61" s="70">
+      <c r="L61" s="69">
         <f>K61+J61+I61</f>
         <v>6.5149999999999997</v>
       </c>
-      <c r="M61" s="69">
+      <c r="M61" s="68">
         <v>2.8</v>
       </c>
-      <c r="N61" s="69">
+      <c r="N61" s="68">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O61" s="69">
+      <c r="O61" s="68">
         <v>2.972826</v>
       </c>
-      <c r="P61" s="70">
+      <c r="P61" s="69">
         <f>O61+N61+M61</f>
         <v>7.9728260000000004</v>
       </c>
-      <c r="Q61" s="69">
+      <c r="Q61" s="68">
         <v>2</v>
       </c>
-      <c r="R61" s="69">
+      <c r="R61" s="68">
         <v>2.2999999999999998</v>
       </c>
-      <c r="S61" s="69">
+      <c r="S61" s="68">
         <v>2.7</v>
       </c>
-      <c r="T61" s="70">
+      <c r="T61" s="69">
         <f>S61+R61+Q61</f>
         <v>7</v>
       </c>
-      <c r="U61" s="69">
+      <c r="U61" s="68">
         <v>3.1</v>
       </c>
-      <c r="V61" s="69">
+      <c r="V61" s="68">
         <v>2.6</v>
       </c>
-      <c r="W61" s="69">
+      <c r="W61" s="68">
         <v>3.04</v>
       </c>
-      <c r="X61" s="70">
+      <c r="X61" s="69">
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="62" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B62" s="186"/>
-      <c r="C62" s="213"/>
-      <c r="D62" s="148"/>
-      <c r="E62" s="218"/>
-      <c r="F62" s="232"/>
-      <c r="G62" s="227"/>
-      <c r="H62" s="123" t="s">
+    <row r="62" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="149"/>
+      <c r="C62" s="147"/>
+      <c r="D62" s="154"/>
+      <c r="E62" s="155"/>
+      <c r="F62" s="140"/>
+      <c r="G62" s="132"/>
+      <c r="H62" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="I62" s="133" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62" s="133"/>
-      <c r="K62" s="133"/>
-      <c r="L62" s="70">
+      <c r="I62" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" s="131"/>
+      <c r="K62" s="131"/>
+      <c r="L62" s="69">
         <v>5</v>
       </c>
-      <c r="M62" s="133" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="133"/>
-      <c r="O62" s="133"/>
-      <c r="P62" s="70">
+      <c r="M62" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="131"/>
+      <c r="O62" s="131"/>
+      <c r="P62" s="69">
         <v>7</v>
       </c>
-      <c r="Q62" s="133" t="s">
-        <v>32</v>
-      </c>
-      <c r="R62" s="133"/>
-      <c r="S62" s="133"/>
-      <c r="T62" s="70">
+      <c r="Q62" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="R62" s="131"/>
+      <c r="S62" s="131"/>
+      <c r="T62" s="69">
         <v>7</v>
       </c>
-      <c r="U62" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="V62" s="119"/>
-      <c r="W62" s="119"/>
-      <c r="X62" s="70">
+      <c r="U62" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="V62" s="120"/>
+      <c r="W62" s="120"/>
+      <c r="X62" s="69">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B63" s="186"/>
-      <c r="C63" s="213"/>
-      <c r="D63" s="148"/>
-      <c r="E63" s="218"/>
-      <c r="F63" s="232"/>
-      <c r="G63" s="227"/>
-      <c r="H63" s="123" t="s">
+    <row r="63" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="149"/>
+      <c r="C63" s="147"/>
+      <c r="D63" s="154"/>
+      <c r="E63" s="155"/>
+      <c r="F63" s="140"/>
+      <c r="G63" s="132"/>
+      <c r="H63" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="119">
+      <c r="I63" s="120">
         <v>1.333</v>
       </c>
-      <c r="J63" s="119">
+      <c r="J63" s="120">
         <v>1.4</v>
       </c>
-      <c r="K63" s="119">
+      <c r="K63" s="120">
         <v>2.5</v>
       </c>
-      <c r="L63" s="90">
+      <c r="L63" s="89">
         <f>K63+J63+I63</f>
         <v>5.2329999999999997</v>
       </c>
-      <c r="M63" s="119">
+      <c r="M63" s="120">
         <v>1.5</v>
       </c>
-      <c r="N63" s="119">
+      <c r="N63" s="120">
         <v>3.2572839999999998</v>
       </c>
-      <c r="O63" s="119">
+      <c r="O63" s="120">
         <v>1.86</v>
       </c>
-      <c r="P63" s="112">
+      <c r="P63" s="111">
         <f>O63+N63+M63</f>
         <v>6.6172839999999997</v>
       </c>
-      <c r="Q63" s="119">
+      <c r="Q63" s="120">
         <v>2.2623000000000002</v>
       </c>
-      <c r="R63" s="119">
+      <c r="R63" s="120">
         <v>2.5099999999999998</v>
       </c>
-      <c r="S63" s="119"/>
-      <c r="T63" s="91">
+      <c r="S63" s="120">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="T63" s="111">
         <f>S63+R63+Q63</f>
-        <v>4.7722999999999995</v>
-      </c>
-      <c r="U63" s="119"/>
-      <c r="V63" s="119"/>
-      <c r="W63" s="119"/>
-      <c r="X63" s="91">
+        <v>6.8223000000000003</v>
+      </c>
+      <c r="U63" s="120"/>
+      <c r="V63" s="120"/>
+      <c r="W63" s="120"/>
+      <c r="X63" s="90">
         <f>W63+V63+U63</f>
         <v>0</v>
       </c>
-      <c r="Y63" s="7" t="s">
+      <c r="Y63" s="54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="149"/>
+      <c r="C64" s="141" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="64" spans="2:25" ht="16.5">
-      <c r="B64" s="186"/>
-      <c r="C64" s="209" t="s">
+      <c r="D64" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="210" t="s">
-        <v>79</v>
-      </c>
-      <c r="E64" s="211">
+      <c r="E64" s="143">
         <f>L64+P64+T64+X64</f>
         <v>-8.4644727175232077</v>
       </c>
-      <c r="F64" s="231">
+      <c r="F64" s="139">
         <f>SUM(L65,P65,T65,X65)</f>
         <v>-7.0189285867816498</v>
       </c>
-      <c r="G64" s="226">
+      <c r="G64" s="130">
         <f>SUM(L66,P66,T66,Q66,X66)</f>
         <v>-6.3300698065453469</v>
       </c>
-      <c r="H64" s="120" t="s">
+      <c r="H64" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="I64" s="71">
+      <c r="I64" s="70">
         <v>-0.5</v>
       </c>
-      <c r="J64" s="71">
+      <c r="J64" s="70">
         <v>-0.5</v>
       </c>
-      <c r="K64" s="71">
+      <c r="K64" s="70">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="L64" s="72">
+      <c r="L64" s="71">
         <f t="shared" ref="L64:L69" si="8">SUM(I64:K64)</f>
         <v>-2.1</v>
       </c>
-      <c r="M64" s="71">
+      <c r="M64" s="70">
         <v>-0.5</v>
       </c>
-      <c r="N64" s="71">
+      <c r="N64" s="70">
         <v>0.1</v>
       </c>
-      <c r="O64" s="71">
+      <c r="O64" s="70">
         <v>-1.5</v>
       </c>
-      <c r="P64" s="72">
+      <c r="P64" s="71">
         <f t="shared" ref="P64:P69" si="9">SUM(M64:O64)</f>
         <v>-1.9</v>
       </c>
-      <c r="Q64" s="71">
+      <c r="Q64" s="70">
         <v>-0.9</v>
       </c>
-      <c r="R64" s="71">
+      <c r="R64" s="70">
         <v>-0.83660522126404935</v>
       </c>
-      <c r="S64" s="71">
+      <c r="S64" s="70">
         <v>-0.41</v>
       </c>
-      <c r="T64" s="72">
+      <c r="T64" s="71">
         <f t="shared" ref="T64:T69" si="10">SUM(Q64:S64)</f>
         <v>-2.1466052212640494</v>
       </c>
-      <c r="U64" s="71">
+      <c r="U64" s="70">
         <v>-0.48</v>
       </c>
-      <c r="V64" s="71">
+      <c r="V64" s="70">
         <v>-0.34</v>
       </c>
-      <c r="W64" s="71">
+      <c r="W64" s="70">
         <v>-1.4978674962591589</v>
       </c>
-      <c r="X64" s="72">
+      <c r="X64" s="71">
         <f t="shared" ref="X64:X69" si="11">SUM(U64:W64)</f>
         <v>-2.3178674962591588</v>
       </c>
     </row>
-    <row r="65" spans="2:24" ht="15.6">
-      <c r="B65" s="186"/>
-      <c r="C65" s="209"/>
-      <c r="D65" s="210"/>
-      <c r="E65" s="211"/>
-      <c r="F65" s="231"/>
-      <c r="G65" s="226"/>
-      <c r="H65" s="120" t="s">
+    <row r="65" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="149"/>
+      <c r="C65" s="141"/>
+      <c r="D65" s="142"/>
+      <c r="E65" s="143"/>
+      <c r="F65" s="139"/>
+      <c r="G65" s="130"/>
+      <c r="H65" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="I65" s="71">
+      <c r="I65" s="70">
         <v>-0.6</v>
       </c>
-      <c r="J65" s="71">
+      <c r="J65" s="70">
         <v>-0.5</v>
       </c>
-      <c r="K65" s="71">
+      <c r="K65" s="70">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="L65" s="72">
+      <c r="L65" s="71">
         <f t="shared" si="8"/>
         <v>-2.2000000000000002</v>
       </c>
-      <c r="M65" s="71">
+      <c r="M65" s="70">
         <v>-0.8</v>
       </c>
-      <c r="N65" s="71">
+      <c r="N65" s="70">
         <v>-0.5</v>
       </c>
-      <c r="O65" s="71">
+      <c r="O65" s="70">
         <v>-0.7</v>
       </c>
-      <c r="P65" s="72">
+      <c r="P65" s="71">
         <f t="shared" si="9"/>
         <v>-2</v>
       </c>
-      <c r="Q65" s="71">
+      <c r="Q65" s="70">
         <v>-0.4710695833326044</v>
       </c>
-      <c r="R65" s="71">
+      <c r="R65" s="70">
         <v>-0.47785080650561662</v>
       </c>
-      <c r="S65" s="71">
+      <c r="S65" s="70">
         <v>-0.56812301870144577</v>
       </c>
-      <c r="T65" s="72">
+      <c r="T65" s="71">
         <f t="shared" si="10"/>
         <v>-1.5170434085396667</v>
       </c>
-      <c r="U65" s="71">
+      <c r="U65" s="70">
         <v>-0.32641448602076573</v>
       </c>
-      <c r="V65" s="71">
+      <c r="V65" s="70">
         <v>-0.37253694072630583</v>
       </c>
-      <c r="W65" s="71">
+      <c r="W65" s="70">
         <v>-0.60293375149491213</v>
       </c>
-      <c r="X65" s="72">
+      <c r="X65" s="71">
         <f t="shared" si="11"/>
         <v>-1.3018851782419838</v>
       </c>
     </row>
-    <row r="66" spans="2:24" ht="16.5">
-      <c r="B66" s="186"/>
-      <c r="C66" s="209"/>
-      <c r="D66" s="210"/>
-      <c r="E66" s="211"/>
-      <c r="F66" s="231"/>
-      <c r="G66" s="226"/>
-      <c r="H66" s="120" t="s">
+    <row r="66" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B66" s="149"/>
+      <c r="C66" s="141"/>
+      <c r="D66" s="142"/>
+      <c r="E66" s="143"/>
+      <c r="F66" s="139"/>
+      <c r="G66" s="130"/>
+      <c r="H66" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="I66" s="81">
+      <c r="I66" s="80">
         <v>-0.8</v>
       </c>
-      <c r="J66" s="81">
+      <c r="J66" s="80">
         <v>-0.8</v>
       </c>
-      <c r="K66" s="88">
+      <c r="K66" s="87">
         <v>-0.5</v>
       </c>
-      <c r="L66" s="96">
+      <c r="L66" s="95">
         <f t="shared" si="8"/>
         <v>-2.1</v>
       </c>
-      <c r="M66" s="88">
+      <c r="M66" s="87">
         <v>-0.6</v>
       </c>
-      <c r="N66" s="81">
+      <c r="N66" s="80">
         <v>-0.9</v>
       </c>
-      <c r="O66" s="88">
+      <c r="O66" s="87">
         <v>-0.27622289841125025</v>
       </c>
-      <c r="P66" s="96">
+      <c r="P66" s="95">
         <f>SUM(M66:O66)</f>
         <v>-1.7762228984112503</v>
       </c>
-      <c r="Q66" s="81">
+      <c r="Q66" s="80">
         <v>-0.98799805081423986</v>
       </c>
-      <c r="R66" s="235">
+      <c r="R66" s="119">
         <v>-0.47785080650561662</v>
       </c>
-      <c r="S66" s="71"/>
-      <c r="T66" s="110">
+      <c r="S66" s="70"/>
+      <c r="T66" s="109">
         <f t="shared" si="10"/>
         <v>-1.4658488573198565</v>
       </c>
-      <c r="U66" s="71"/>
-      <c r="V66" s="71"/>
-      <c r="W66" s="71"/>
-      <c r="X66" s="110">
+      <c r="U66" s="70"/>
+      <c r="V66" s="70"/>
+      <c r="W66" s="70"/>
+      <c r="X66" s="109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:24" ht="15" customHeight="1">
-      <c r="B67" s="186"/>
-      <c r="C67" s="215" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" s="216" t="s">
+    <row r="67" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="149"/>
+      <c r="C67" s="151" t="s">
         <v>79</v>
       </c>
-      <c r="E67" s="217">
+      <c r="D67" s="152" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="153">
         <f>L67+P67+T67+X67</f>
         <v>-20.34262829557931</v>
       </c>
-      <c r="F67" s="222">
+      <c r="F67" s="126">
         <f>SUM(L68,P68,T68,X68)</f>
         <v>-24.141371751369434</v>
       </c>
-      <c r="G67" s="225">
+      <c r="G67" s="129">
         <f>SUM(L69,P69,T69,X69)</f>
         <v>-16.595412480713406</v>
       </c>
-      <c r="H67" s="122" t="s">
+      <c r="H67" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="I67" s="73">
+      <c r="I67" s="72">
         <v>-1.3</v>
       </c>
-      <c r="J67" s="73">
+      <c r="J67" s="72">
         <v>-1.8</v>
       </c>
-      <c r="K67" s="73">
+      <c r="K67" s="72">
         <v>-1.2</v>
       </c>
-      <c r="L67" s="74">
+      <c r="L67" s="73">
         <f t="shared" si="8"/>
         <v>-4.3</v>
       </c>
-      <c r="M67" s="73">
+      <c r="M67" s="72">
         <v>-1.6</v>
       </c>
-      <c r="N67" s="73">
+      <c r="N67" s="72">
         <v>-1.4</v>
       </c>
-      <c r="O67" s="73">
+      <c r="O67" s="72">
         <v>-1.5</v>
       </c>
-      <c r="P67" s="74">
+      <c r="P67" s="73">
         <f t="shared" si="9"/>
         <v>-4.5</v>
       </c>
-      <c r="Q67" s="73">
+      <c r="Q67" s="72">
         <v>-1.91</v>
       </c>
-      <c r="R67" s="73">
+      <c r="R67" s="72">
         <v>-2.3939222677777598</v>
       </c>
-      <c r="S67" s="73">
+      <c r="S67" s="72">
         <v>-2.1</v>
       </c>
-      <c r="T67" s="74">
+      <c r="T67" s="73">
         <f t="shared" si="10"/>
         <v>-6.4039222677777605</v>
       </c>
-      <c r="U67" s="73">
+      <c r="U67" s="72">
         <v>-1.71</v>
       </c>
-      <c r="V67" s="73">
+      <c r="V67" s="72">
         <v>-1.76033753077637</v>
       </c>
-      <c r="W67" s="73">
+      <c r="W67" s="72">
         <v>-1.66836849702518</v>
       </c>
-      <c r="X67" s="74">
+      <c r="X67" s="73">
         <f t="shared" si="11"/>
         <v>-5.1387060278015504</v>
       </c>
     </row>
-    <row r="68" spans="2:24" ht="15" customHeight="1">
-      <c r="B68" s="186"/>
-      <c r="C68" s="215"/>
-      <c r="D68" s="216"/>
-      <c r="E68" s="217"/>
-      <c r="F68" s="223"/>
-      <c r="G68" s="225"/>
-      <c r="H68" s="122" t="s">
+    <row r="68" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="149"/>
+      <c r="C68" s="151"/>
+      <c r="D68" s="152"/>
+      <c r="E68" s="153"/>
+      <c r="F68" s="127"/>
+      <c r="G68" s="129"/>
+      <c r="H68" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="I68" s="73">
+      <c r="I68" s="72">
         <v>-2.1</v>
       </c>
-      <c r="J68" s="73">
+      <c r="J68" s="72">
         <v>-2.1</v>
       </c>
-      <c r="K68" s="73">
+      <c r="K68" s="72">
         <v>-2.1</v>
       </c>
-      <c r="L68" s="74">
+      <c r="L68" s="73">
         <f t="shared" si="8"/>
         <v>-6.3000000000000007</v>
       </c>
-      <c r="M68" s="73">
+      <c r="M68" s="72">
         <v>-1.7</v>
       </c>
-      <c r="N68" s="73">
+      <c r="N68" s="72">
         <v>-1.7</v>
       </c>
-      <c r="O68" s="73">
+      <c r="O68" s="72">
         <v>-1.7</v>
       </c>
-      <c r="P68" s="74">
+      <c r="P68" s="73">
         <f t="shared" si="9"/>
         <v>-5.0999999999999996</v>
       </c>
-      <c r="Q68" s="73">
+      <c r="Q68" s="72">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="R68" s="73">
+      <c r="R68" s="72">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="S68" s="73">
+      <c r="S68" s="72">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="T68" s="74">
+      <c r="T68" s="73">
         <f t="shared" si="10"/>
         <v>-6.5766783756847165</v>
       </c>
-      <c r="U68" s="73">
+      <c r="U68" s="72">
         <v>-2.0548977918949052</v>
       </c>
-      <c r="V68" s="73">
+      <c r="V68" s="72">
         <v>-2.0548977918949052</v>
       </c>
-      <c r="W68" s="73">
+      <c r="W68" s="72">
         <v>-2.0548977918949052</v>
       </c>
-      <c r="X68" s="74">
+      <c r="X68" s="73">
         <f t="shared" si="11"/>
         <v>-6.1646933756847151</v>
       </c>
     </row>
-    <row r="69" spans="2:24" ht="15" customHeight="1">
-      <c r="B69" s="214"/>
-      <c r="C69" s="215"/>
-      <c r="D69" s="216"/>
-      <c r="E69" s="217"/>
-      <c r="F69" s="224"/>
-      <c r="G69" s="225"/>
-      <c r="H69" s="122" t="s">
+    <row r="69" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="150"/>
+      <c r="C69" s="151"/>
+      <c r="D69" s="152"/>
+      <c r="E69" s="153"/>
+      <c r="F69" s="128"/>
+      <c r="G69" s="129"/>
+      <c r="H69" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="I69" s="88">
+      <c r="I69" s="87">
         <v>-0.9</v>
       </c>
-      <c r="J69" s="88">
+      <c r="J69" s="87">
         <v>-2</v>
       </c>
-      <c r="K69" s="88">
+      <c r="K69" s="87">
         <v>-2.1</v>
       </c>
-      <c r="L69" s="96">
+      <c r="L69" s="95">
         <f t="shared" si="8"/>
         <v>-5</v>
       </c>
-      <c r="M69" s="88">
+      <c r="M69" s="87">
         <v>-0.3</v>
       </c>
-      <c r="N69" s="81">
+      <c r="N69" s="80">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="O69" s="88">
+      <c r="O69" s="87">
         <v>-1.4</v>
       </c>
-      <c r="P69" s="114">
+      <c r="P69" s="113">
         <f t="shared" si="9"/>
         <v>-6.6</v>
       </c>
-      <c r="Q69" s="81">
+      <c r="Q69" s="80">
         <v>-2.8031863554851699</v>
       </c>
-      <c r="R69" s="235">
+      <c r="R69" s="119">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="S69" s="73"/>
-      <c r="T69" s="111">
+      <c r="S69" s="72"/>
+      <c r="T69" s="110">
         <f t="shared" si="10"/>
         <v>-4.9954124807134086</v>
       </c>
-      <c r="U69" s="73"/>
-      <c r="V69" s="73"/>
-      <c r="W69" s="73"/>
-      <c r="X69" s="111">
+      <c r="U69" s="72"/>
+      <c r="V69" s="72"/>
+      <c r="W69" s="72"/>
+      <c r="X69" s="110">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="14:14" ht="15" customHeight="1">
+    <row r="94" spans="14:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N94" s="40">
         <f>SUM(L66:N66)-SUM(L65:N65)</f>
         <v>-0.10000000000000009</v>
       </c>
     </row>
-    <row r="95" spans="14:14" ht="15" customHeight="1">
+    <row r="95" spans="14:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N95" s="40">
         <f>SUM(L69:N69)-SUM(L68:N68)</f>
         <v>-0.5</v>
@@ -6527,31 +6598,84 @@
     </row>
   </sheetData>
   <mergeCells count="127">
-    <mergeCell ref="F67:F69"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="M62:O62"/>
-    <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="F58:F60"/>
-    <mergeCell ref="G58:G60"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="F64:F66"/>
-    <mergeCell ref="F61:F63"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="E64:E66"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="B61:B69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="D67:D69"/>
-    <mergeCell ref="E67:E69"/>
-    <mergeCell ref="D61:D63"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="U56:W56"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="U53:W53"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="I2:X2"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="F13:F15"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="C58:C60"/>
@@ -6576,84 +6700,31 @@
     <mergeCell ref="B4:B18"/>
     <mergeCell ref="C31:C33"/>
     <mergeCell ref="C10:C12"/>
-    <mergeCell ref="I2:X2"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="U56:W56"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="Q53:S53"/>
-    <mergeCell ref="U53:W53"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="B61:B69"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="F67:F69"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="F58:F60"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="F61:F63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6664,7 +6735,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE1562A-E356-4B2D-A63C-39D2CDCD6A5B}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.5703125" style="31" customWidth="1"/>
     <col min="2" max="2" width="77.5703125" style="31" customWidth="1"/>
@@ -6672,119 +6743,119 @@
     <col min="4" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="32" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.9">
-      <c r="A3" s="31" t="s">
+      <c r="B3" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="31" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="41" t="s">
+      <c r="B4" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="41" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.9">
-      <c r="A5" s="41" t="s">
+      <c r="B5" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="41" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="61" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="61" t="s">
+      <c r="B6" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="61" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="31" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="62" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.6">
-      <c r="A8" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="63"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="30"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
     </row>
-    <row r="9" spans="1:6" ht="15.6">
-      <c r="A9" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="63"/>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="62"/>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
     </row>
-    <row r="10" spans="1:6" ht="78">
+    <row r="10" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="42" t="s">
         <v>95</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>96</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
     </row>
-    <row r="11" spans="1:6" ht="46.9">
+    <row r="11" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="42" t="s">
         <v>97</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>98</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
     </row>
-    <row r="12" spans="1:6" ht="15.6">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="30"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="30"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="61" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.6">
-      <c r="A14" s="31" t="s">
-        <v>101</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6795,299 +6866,299 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DB5036-8F66-4319-848F-CAD3FAB6DF02}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="B2" s="4" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" outlineLevel="1">
+    </row>
+    <row r="4" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" outlineLevel="1">
-      <c r="B5" t="s">
+      <c r="C5" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:6" outlineLevel="1">
+    <row r="6" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:6" outlineLevel="1">
+    <row r="7" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:6" outlineLevel="1">
+    <row r="8" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:6" outlineLevel="1">
+    <row r="9" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:6" outlineLevel="1">
+    <row r="10" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
       <c r="B10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:6" outlineLevel="1">
+    <row r="11" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
       <c r="B11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:6" outlineLevel="1">
+    <row r="12" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>4</v>
       </c>
       <c r="B12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:6" outlineLevel="1">
+    <row r="13" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:6" outlineLevel="1">
+    <row r="14" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>6</v>
       </c>
       <c r="B14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:6" outlineLevel="1">
+    <row r="15" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>7</v>
       </c>
       <c r="B15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:6" outlineLevel="1">
+    <row r="16" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>8</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" outlineLevel="1">
+    <row r="17" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9</v>
       </c>
       <c r="B17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" outlineLevel="1">
+    <row r="18" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>10</v>
       </c>
       <c r="B18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" outlineLevel="1">
+    <row r="19" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>11</v>
       </c>
       <c r="B19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" outlineLevel="1">
+    <row r="20" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>12</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" outlineLevel="1">
+    <row r="21" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>13</v>
       </c>
       <c r="B21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" outlineLevel="1">
+    <row r="22" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>14</v>
       </c>
       <c r="B22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" outlineLevel="1">
+    <row r="23" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>15</v>
       </c>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" outlineLevel="1">
+    <row r="24" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>16</v>
       </c>
       <c r="B24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" outlineLevel="1">
+    <row r="25" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>17</v>
       </c>
       <c r="B25" s="2"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026 Bowler Chart - OFS Training.xlsx
+++ b/data/2026 Bowler Chart - OFS Training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\210077026\Box\OFS Global Technical Training @OFFICIAL NEW\Leadership Team\Bowler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\605014645\Box\OFS Global Technical Training @OFFICIAL NEW\Leadership Team\Bowler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767FFC3A-EA5D-4896-8768-4FAEF23DC63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA08E1B-1833-4B3C-AF63-A51A4D45C3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="601" xr2:uid="{8476BB21-6D10-4BB9-B6CE-FEFD481D0662}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="601" xr2:uid="{8476BB21-6D10-4BB9-B6CE-FEFD481D0662}"/>
   </bookViews>
   <sheets>
     <sheet name="Bowler L1 Training" sheetId="16" r:id="rId1"/>
@@ -564,42 +564,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="R66" authorId="1" shapeId="0" xr:uid="{9B4E6628-812D-4C80-9A15-B8DCCE20236A}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Jen Wright:
-Holding to plan - don't have visibility to August actuals  yet</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R69" authorId="1" shapeId="0" xr:uid="{8CE9D396-21E5-463C-8F92-EFD21B3F62A3}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Jen Wright:
-Holding to plan - don't have visibility to August actuals  yet</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="116">
   <si>
     <t>Level 2</t>
   </si>
@@ -750,6 +720,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(i.e. final assessment scores)</t>
     </r>
@@ -980,7 +951,7 @@
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1007,94 +978,111 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF444444"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <strike/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1160,15 +1148,9 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1374,7 +1356,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -1499,9 +1481,6 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1509,9 +1488,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="22" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1680,12 +1656,6 @@
     <xf numFmtId="1" fontId="28" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="28" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1707,29 +1677,332 @@
     <xf numFmtId="9" fontId="27" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="37" fontId="6" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="37" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="10" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="28" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="22" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1740,326 +2013,41 @@
     <xf numFmtId="167" fontId="22" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="30" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="21" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="39" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2067,7 +2055,58 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2492,24 +2531,24 @@
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="182">
+      <c r="I2" s="171">
         <v>2026</v>
       </c>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
-      <c r="M2" s="183"/>
-      <c r="N2" s="183"/>
-      <c r="O2" s="183"/>
-      <c r="P2" s="183"/>
-      <c r="Q2" s="183"/>
-      <c r="R2" s="183"/>
-      <c r="S2" s="183"/>
-      <c r="T2" s="183"/>
-      <c r="U2" s="183"/>
-      <c r="V2" s="183"/>
-      <c r="W2" s="183"/>
-      <c r="X2" s="184"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="172"/>
+      <c r="U2" s="172"/>
+      <c r="V2" s="172"/>
+      <c r="W2" s="172"/>
+      <c r="X2" s="173"/>
     </row>
     <row r="3" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -2582,23 +2621,23 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="163" t="s">
+      <c r="B4" s="194" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="178" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="188" t="s">
+      <c r="D4" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="189">
+      <c r="E4" s="180">
         <f>SUM(L4,P4,T4,X4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="192">
-        <v>0</v>
-      </c>
-      <c r="G4" s="191">
+      <c r="F4" s="126">
+        <v>0</v>
+      </c>
+      <c r="G4" s="181">
         <f>SUM(L6,P6,T6,X6)</f>
         <v>1</v>
       </c>
@@ -2659,12 +2698,12 @@
       </c>
     </row>
     <row r="5" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="163"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="191"/>
+      <c r="B5" s="194"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="180"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="181"/>
       <c r="H5" s="11" t="s">
         <v>27</v>
       </c>
@@ -2722,53 +2761,57 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="163"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="189"/>
-      <c r="F6" s="192"/>
-      <c r="G6" s="191"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="180"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="181"/>
       <c r="H6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="85">
-        <v>0</v>
-      </c>
-      <c r="J6" s="85">
-        <v>0</v>
-      </c>
-      <c r="K6" s="85">
-        <v>0</v>
-      </c>
-      <c r="L6" s="96">
+      <c r="I6" s="83">
+        <v>0</v>
+      </c>
+      <c r="J6" s="83">
+        <v>0</v>
+      </c>
+      <c r="K6" s="83">
+        <v>0</v>
+      </c>
+      <c r="L6" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M6" s="85">
-        <v>0</v>
-      </c>
-      <c r="N6" s="85">
-        <v>0</v>
-      </c>
-      <c r="O6" s="114">
-        <v>0</v>
-      </c>
-      <c r="P6" s="96">
+      <c r="M6" s="83">
+        <v>0</v>
+      </c>
+      <c r="N6" s="83">
+        <v>0</v>
+      </c>
+      <c r="O6" s="110">
+        <v>0</v>
+      </c>
+      <c r="P6" s="94">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="115">
+      <c r="Q6" s="111">
         <v>1</v>
       </c>
-      <c r="R6" s="85">
-        <v>0</v>
-      </c>
-      <c r="S6" s="14"/>
-      <c r="T6" s="13">
+      <c r="R6" s="83">
+        <v>0</v>
+      </c>
+      <c r="S6" s="83">
+        <v>0</v>
+      </c>
+      <c r="T6" s="122">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U6" s="14"/>
+      <c r="U6" s="83">
+        <v>0</v>
+      </c>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
       <c r="X6" s="13">
@@ -2777,23 +2820,23 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="163"/>
-      <c r="C7" s="144" t="s">
+      <c r="B7" s="194"/>
+      <c r="C7" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="203">
-        <v>0</v>
-      </c>
-      <c r="F7" s="193">
-        <v>0</v>
-      </c>
-      <c r="G7" s="196">
-        <v>0.95</v>
-      </c>
-      <c r="H7" s="122" t="s">
+      <c r="E7" s="165">
+        <v>0</v>
+      </c>
+      <c r="F7" s="182">
+        <v>0</v>
+      </c>
+      <c r="G7" s="184">
+        <v>1</v>
+      </c>
+      <c r="H7" s="118" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="15">
@@ -2846,13 +2889,13 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="163"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="204"/>
-      <c r="F8" s="193"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="122" t="s">
+      <c r="B8" s="194"/>
+      <c r="C8" s="129"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="118" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="15">
@@ -2905,69 +2948,75 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="163"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="193"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="122" t="s">
+      <c r="B9" s="194"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="182"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="84">
-        <v>0</v>
-      </c>
-      <c r="J9" s="84">
-        <v>0</v>
-      </c>
-      <c r="K9" s="84">
-        <v>0</v>
-      </c>
-      <c r="L9" s="96">
-        <v>0</v>
-      </c>
-      <c r="M9" s="84">
-        <v>0</v>
-      </c>
-      <c r="N9" s="84">
-        <v>0</v>
-      </c>
-      <c r="O9" s="84">
-        <v>0</v>
-      </c>
-      <c r="P9" s="96">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="116">
+      <c r="I9" s="82">
+        <v>0</v>
+      </c>
+      <c r="J9" s="82">
+        <v>0</v>
+      </c>
+      <c r="K9" s="82">
+        <v>0</v>
+      </c>
+      <c r="L9" s="94">
+        <v>0</v>
+      </c>
+      <c r="M9" s="82">
+        <v>0</v>
+      </c>
+      <c r="N9" s="82">
+        <v>0</v>
+      </c>
+      <c r="O9" s="82">
+        <v>0</v>
+      </c>
+      <c r="P9" s="94">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="112">
         <v>1.089</v>
       </c>
-      <c r="R9" s="118">
-        <v>0.95</v>
-      </c>
-      <c r="S9" s="45"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="45"/>
+      <c r="R9" s="121">
+        <v>1</v>
+      </c>
+      <c r="S9" s="111">
+        <v>1</v>
+      </c>
+      <c r="T9" s="122">
+        <v>1</v>
+      </c>
+      <c r="U9" s="111">
+        <v>1</v>
+      </c>
       <c r="V9" s="45"/>
       <c r="W9" s="17"/>
       <c r="X9" s="16"/>
     </row>
     <row r="10" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="163"/>
-      <c r="C10" s="181" t="s">
+      <c r="B10" s="194"/>
+      <c r="C10" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="188" t="s">
+      <c r="D10" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="202">
+      <c r="E10" s="135">
         <f>SUM(L10,P10,T10,X10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="192">
+      <c r="F10" s="126">
         <f>SUM(L11,P11,T11,X11)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="189">
+      <c r="G10" s="180">
         <f>SUM(L12,P12,T12,X12)</f>
         <v>0</v>
       </c>
@@ -3028,12 +3077,12 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="163"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="188"/>
-      <c r="E11" s="202"/>
-      <c r="F11" s="192"/>
-      <c r="G11" s="189"/>
+      <c r="B11" s="194"/>
+      <c r="C11" s="178"/>
+      <c r="D11" s="164"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="180"/>
       <c r="H11" s="11" t="s">
         <v>27</v>
       </c>
@@ -3091,53 +3140,57 @@
       </c>
     </row>
     <row r="12" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="163"/>
-      <c r="C12" s="181"/>
-      <c r="D12" s="188"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="192"/>
-      <c r="G12" s="189"/>
+      <c r="B12" s="194"/>
+      <c r="C12" s="178"/>
+      <c r="D12" s="164"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="180"/>
       <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="85">
-        <v>0</v>
-      </c>
-      <c r="J12" s="85">
-        <v>0</v>
-      </c>
-      <c r="K12" s="85">
-        <v>0</v>
-      </c>
-      <c r="L12" s="96">
+      <c r="I12" s="83">
+        <v>0</v>
+      </c>
+      <c r="J12" s="83">
+        <v>0</v>
+      </c>
+      <c r="K12" s="83">
+        <v>0</v>
+      </c>
+      <c r="L12" s="94">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="85">
-        <v>0</v>
-      </c>
-      <c r="N12" s="85">
-        <v>0</v>
-      </c>
-      <c r="O12" s="85">
-        <v>0</v>
-      </c>
-      <c r="P12" s="96">
+      <c r="M12" s="83">
+        <v>0</v>
+      </c>
+      <c r="N12" s="83">
+        <v>0</v>
+      </c>
+      <c r="O12" s="83">
+        <v>0</v>
+      </c>
+      <c r="P12" s="94">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="85">
-        <v>0</v>
-      </c>
-      <c r="R12" s="85">
-        <v>0</v>
-      </c>
-      <c r="S12" s="14"/>
-      <c r="T12" s="13">
+      <c r="Q12" s="83">
+        <v>0</v>
+      </c>
+      <c r="R12" s="83">
+        <v>0</v>
+      </c>
+      <c r="S12" s="83">
+        <v>0</v>
+      </c>
+      <c r="T12" s="94">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U12" s="14"/>
+      <c r="U12" s="83">
+        <v>0</v>
+      </c>
       <c r="V12" s="14"/>
       <c r="W12" s="14"/>
       <c r="X12" s="13">
@@ -3146,23 +3199,23 @@
       </c>
     </row>
     <row r="13" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="163"/>
-      <c r="C13" s="144" t="s">
+      <c r="B13" s="194"/>
+      <c r="C13" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="171" t="s">
+      <c r="D13" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="156">
+      <c r="E13" s="179">
         <v>1</v>
       </c>
-      <c r="F13" s="201">
-        <v>0.9</v>
-      </c>
-      <c r="G13" s="156">
-        <v>0.9</v>
-      </c>
-      <c r="H13" s="122" t="s">
+      <c r="F13" s="143">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="179">
+        <v>0.9</v>
+      </c>
+      <c r="H13" s="118" t="s">
         <v>26</v>
       </c>
       <c r="I13" s="15" t="s">
@@ -3215,13 +3268,13 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="163"/>
-      <c r="C14" s="144"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="201"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="122" t="s">
+      <c r="B14" s="194"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="179"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="179"/>
+      <c r="H14" s="118" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="38">
@@ -3233,7 +3286,7 @@
       <c r="K14" s="38">
         <v>0.9</v>
       </c>
-      <c r="L14" s="91">
+      <c r="L14" s="89">
         <v>0.9</v>
       </c>
       <c r="M14" s="38">
@@ -3274,492 +3327,504 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="163"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="201"/>
-      <c r="G15" s="156"/>
-      <c r="H15" s="122" t="s">
+      <c r="B15" s="194"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="75">
-        <v>0.9</v>
-      </c>
-      <c r="J15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="75" t="s">
+      <c r="I15" s="73">
+        <v>0.9</v>
+      </c>
+      <c r="J15" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="86">
-        <v>0.9</v>
-      </c>
-      <c r="M15" s="75">
-        <v>0.9</v>
-      </c>
-      <c r="N15" s="75">
-        <v>0.9</v>
-      </c>
-      <c r="O15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="86">
-        <v>0.9</v>
-      </c>
-      <c r="Q15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="S15" s="47"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="49"/>
+      <c r="L15" s="84">
+        <v>0.9</v>
+      </c>
+      <c r="M15" s="73">
+        <v>0.9</v>
+      </c>
+      <c r="N15" s="73">
+        <v>0.9</v>
+      </c>
+      <c r="O15" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="84">
+        <v>0.9</v>
+      </c>
+      <c r="Q15" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" s="48"/>
       <c r="W15" s="17"/>
       <c r="X15" s="16"/>
     </row>
     <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="163"/>
-      <c r="C16" s="206" t="s">
+      <c r="B16" s="194"/>
+      <c r="C16" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="190" t="s">
+      <c r="D16" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="192" t="s">
+      <c r="E16" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="194">
-        <v>0.9</v>
-      </c>
-      <c r="G16" s="199">
+      <c r="F16" s="155">
+        <v>0.9</v>
+      </c>
+      <c r="G16" s="152">
+        <v>1</v>
+      </c>
+      <c r="H16" s="117" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="V16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="W16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="X16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y16" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="194"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="155"/>
+      <c r="G17" s="152"/>
+      <c r="H17" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="J17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="K17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="L17" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="M17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="N17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="O17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="P17" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="R17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="S17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="T17" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="U17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="V17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="W17" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="X17" s="23">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="194"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="169"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="117" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="81">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="J18" s="73">
+        <v>0.9</v>
+      </c>
+      <c r="K18" s="81">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="L18" s="90">
+        <v>0.92</v>
+      </c>
+      <c r="M18" s="81">
+        <v>1</v>
+      </c>
+      <c r="N18" s="81">
+        <v>1</v>
+      </c>
+      <c r="O18" s="100">
+        <v>84.6</v>
+      </c>
+      <c r="P18" s="90">
         <v>0.95</v>
       </c>
-      <c r="H16" s="121" t="s">
+      <c r="Q18" s="81">
+        <v>1</v>
+      </c>
+      <c r="R18" s="113">
+        <v>1</v>
+      </c>
+      <c r="S18" s="113">
+        <v>1</v>
+      </c>
+      <c r="T18" s="123">
+        <v>1</v>
+      </c>
+      <c r="U18" s="113">
+        <v>1</v>
+      </c>
+      <c r="V18" s="51"/>
+      <c r="W18" s="51"/>
+      <c r="X18" s="43"/>
+    </row>
+    <row r="19" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="194" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="130" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="124">
+        <v>83</v>
+      </c>
+      <c r="F19" s="141">
+        <v>83</v>
+      </c>
+      <c r="G19" s="124">
+        <v>84.4</v>
+      </c>
+      <c r="H19" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="O16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="P16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="T16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="U16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="V16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="W16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="X16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y16" s="54" t="s">
+      <c r="I19" s="53">
+        <v>80.3</v>
+      </c>
+      <c r="J19" s="53">
+        <v>89.2</v>
+      </c>
+      <c r="K19" s="53">
+        <v>81</v>
+      </c>
+      <c r="L19" s="54">
+        <v>83</v>
+      </c>
+      <c r="M19" s="53">
+        <v>88.6</v>
+      </c>
+      <c r="N19" s="53">
+        <v>86</v>
+      </c>
+      <c r="O19" s="53">
+        <v>82.7</v>
+      </c>
+      <c r="P19" s="54">
+        <v>86.3</v>
+      </c>
+      <c r="Q19" s="53">
+        <v>82</v>
+      </c>
+      <c r="R19" s="53">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="S19" s="53">
+        <v>83.2</v>
+      </c>
+      <c r="T19" s="54">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="U19" s="53">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="V19" s="53">
+        <v>83.6</v>
+      </c>
+      <c r="W19" s="53">
+        <v>72.8</v>
+      </c>
+      <c r="X19" s="54">
+        <v>80.099999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="194"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="53">
+        <v>83</v>
+      </c>
+      <c r="J20" s="53">
+        <v>83</v>
+      </c>
+      <c r="K20" s="53">
+        <v>83</v>
+      </c>
+      <c r="L20" s="54">
+        <v>83</v>
+      </c>
+      <c r="M20" s="53">
+        <v>83</v>
+      </c>
+      <c r="N20" s="53">
+        <v>83</v>
+      </c>
+      <c r="O20" s="53">
+        <v>83</v>
+      </c>
+      <c r="P20" s="54">
+        <v>83</v>
+      </c>
+      <c r="Q20" s="53">
+        <v>83</v>
+      </c>
+      <c r="R20" s="53">
+        <v>83</v>
+      </c>
+      <c r="S20" s="53">
+        <v>83</v>
+      </c>
+      <c r="T20" s="54">
+        <v>83</v>
+      </c>
+      <c r="U20" s="53">
+        <v>83</v>
+      </c>
+      <c r="V20" s="53">
+        <v>83</v>
+      </c>
+      <c r="W20" s="53">
+        <v>83</v>
+      </c>
+      <c r="X20" s="54">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="194"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="118" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="72">
+        <v>79</v>
+      </c>
+      <c r="J21" s="80">
+        <v>84</v>
+      </c>
+      <c r="K21" s="80">
+        <v>87</v>
+      </c>
+      <c r="L21" s="86">
+        <v>85</v>
+      </c>
+      <c r="M21" s="72">
+        <v>79</v>
+      </c>
+      <c r="N21" s="101">
+        <v>91</v>
+      </c>
+      <c r="O21" s="72">
+        <v>75.8</v>
+      </c>
+      <c r="P21" s="86">
+        <v>84.4</v>
+      </c>
+      <c r="Q21" s="101">
+        <v>84.7</v>
+      </c>
+      <c r="R21" s="72">
+        <v>82.9</v>
+      </c>
+      <c r="S21" s="101">
+        <v>91.3</v>
+      </c>
+      <c r="T21" s="86">
+        <v>86.2</v>
+      </c>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
+      <c r="W21" s="55"/>
+      <c r="X21" s="44"/>
+    </row>
+    <row r="22" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="194"/>
+      <c r="C22" s="127" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="168" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="170" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="126">
+        <v>55</v>
+      </c>
+      <c r="G22" s="135">
+        <f>SUM(L24,P24,T24,X24)</f>
+        <v>79</v>
+      </c>
+      <c r="H22" s="117" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="W22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="X22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y22" s="52" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="163"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="190"/>
-      <c r="E17" s="192"/>
-      <c r="F17" s="194"/>
-      <c r="G17" s="199"/>
-      <c r="H17" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="J17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="K17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="L17" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="M17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="N17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="O17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="P17" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="R17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="S17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="T17" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="U17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="V17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="W17" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="X17" s="23">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="163"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="190"/>
-      <c r="E18" s="192"/>
-      <c r="F18" s="195"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="121" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="83">
-        <v>0.92300000000000004</v>
-      </c>
-      <c r="J18" s="75">
-        <v>0.9</v>
-      </c>
-      <c r="K18" s="83">
-        <v>0.92300000000000004</v>
-      </c>
-      <c r="L18" s="92">
-        <v>0.92</v>
-      </c>
-      <c r="M18" s="83">
-        <v>1</v>
-      </c>
-      <c r="N18" s="83">
-        <v>1</v>
-      </c>
-      <c r="O18" s="102">
-        <v>84.6</v>
-      </c>
-      <c r="P18" s="92">
-        <v>0.95</v>
-      </c>
-      <c r="Q18" s="83">
-        <v>1</v>
-      </c>
-      <c r="R18" s="117">
-        <v>1</v>
-      </c>
-      <c r="S18" s="52"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="52"/>
-      <c r="V18" s="53"/>
-      <c r="W18" s="53"/>
-      <c r="X18" s="43"/>
-    </row>
-    <row r="19" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="163" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="144" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="171" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="219">
-        <v>83</v>
-      </c>
-      <c r="F19" s="229">
-        <v>83</v>
-      </c>
-      <c r="G19" s="219">
-        <v>84.4</v>
-      </c>
-      <c r="H19" s="122" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="55">
-        <v>80.3</v>
-      </c>
-      <c r="J19" s="55">
-        <v>89.2</v>
-      </c>
-      <c r="K19" s="55">
-        <v>81</v>
-      </c>
-      <c r="L19" s="56">
-        <v>83</v>
-      </c>
-      <c r="M19" s="55">
-        <v>88.6</v>
-      </c>
-      <c r="N19" s="55">
-        <v>86</v>
-      </c>
-      <c r="O19" s="55">
-        <v>82.7</v>
-      </c>
-      <c r="P19" s="56">
-        <v>86.3</v>
-      </c>
-      <c r="Q19" s="55">
-        <v>82</v>
-      </c>
-      <c r="R19" s="55">
-        <v>79.400000000000006</v>
-      </c>
-      <c r="S19" s="55">
-        <v>83.2</v>
-      </c>
-      <c r="T19" s="56">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="U19" s="55">
-        <v>79.099999999999994</v>
-      </c>
-      <c r="V19" s="55">
-        <v>83.6</v>
-      </c>
-      <c r="W19" s="55">
-        <v>72.8</v>
-      </c>
-      <c r="X19" s="56">
-        <v>80.099999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="163"/>
-      <c r="C20" s="144"/>
-      <c r="D20" s="171"/>
-      <c r="E20" s="220"/>
-      <c r="F20" s="230"/>
-      <c r="G20" s="220"/>
-      <c r="H20" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" s="55">
-        <v>83</v>
-      </c>
-      <c r="J20" s="55">
-        <v>83</v>
-      </c>
-      <c r="K20" s="55">
-        <v>83</v>
-      </c>
-      <c r="L20" s="56">
-        <v>83</v>
-      </c>
-      <c r="M20" s="55">
-        <v>83</v>
-      </c>
-      <c r="N20" s="55">
-        <v>83</v>
-      </c>
-      <c r="O20" s="55">
-        <v>83</v>
-      </c>
-      <c r="P20" s="56">
-        <v>83</v>
-      </c>
-      <c r="Q20" s="55">
-        <v>83</v>
-      </c>
-      <c r="R20" s="55">
-        <v>83</v>
-      </c>
-      <c r="S20" s="55">
-        <v>83</v>
-      </c>
-      <c r="T20" s="56">
-        <v>83</v>
-      </c>
-      <c r="U20" s="55">
-        <v>83</v>
-      </c>
-      <c r="V20" s="55">
-        <v>83</v>
-      </c>
-      <c r="W20" s="55">
-        <v>83</v>
-      </c>
-      <c r="X20" s="56">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="163"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="171"/>
-      <c r="E21" s="220"/>
-      <c r="F21" s="230"/>
-      <c r="G21" s="220"/>
-      <c r="H21" s="122" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="74">
-        <v>79</v>
-      </c>
-      <c r="J21" s="82">
-        <v>84</v>
-      </c>
-      <c r="K21" s="82">
-        <v>87</v>
-      </c>
-      <c r="L21" s="88">
-        <v>85</v>
-      </c>
-      <c r="M21" s="74">
-        <v>79</v>
-      </c>
-      <c r="N21" s="103">
-        <v>91</v>
-      </c>
-      <c r="O21" s="74">
-        <v>75.8</v>
-      </c>
-      <c r="P21" s="88">
-        <v>84.4</v>
-      </c>
-      <c r="Q21" s="103">
-        <v>84.7</v>
-      </c>
-      <c r="R21" s="74">
-        <v>82.9</v>
-      </c>
-      <c r="S21" s="103">
-        <v>91.3</v>
-      </c>
-      <c r="T21" s="88">
-        <v>86.2</v>
-      </c>
-      <c r="U21" s="57"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="44"/>
-    </row>
-    <row r="22" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="163"/>
-      <c r="C22" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="207" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="208" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="192">
-        <v>55</v>
-      </c>
-      <c r="G22" s="202">
-        <f>SUM(L24,P24,T24,X24)</f>
-        <v>78</v>
-      </c>
-      <c r="H22" s="121" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="O22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="S22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="T22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="U22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="V22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="W22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="X22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y22" s="54" t="s">
-        <v>36</v>
-      </c>
-    </row>
     <row r="23" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="163"/>
-      <c r="C23" s="164"/>
-      <c r="D23" s="190"/>
-      <c r="E23" s="208"/>
-      <c r="F23" s="192"/>
-      <c r="G23" s="202"/>
-      <c r="H23" s="121" t="s">
+      <c r="B23" s="194"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="117" t="s">
         <v>27</v>
       </c>
       <c r="I23" s="12">
@@ -3812,78 +3877,80 @@
       </c>
     </row>
     <row r="24" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="163"/>
-      <c r="C24" s="164"/>
-      <c r="D24" s="190"/>
-      <c r="E24" s="208"/>
-      <c r="F24" s="192"/>
-      <c r="G24" s="202"/>
-      <c r="H24" s="121" t="s">
+      <c r="B24" s="194"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="169"/>
+      <c r="E24" s="170"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="84">
+      <c r="I24" s="82">
         <v>2</v>
       </c>
-      <c r="J24" s="82">
+      <c r="J24" s="80">
         <v>5</v>
       </c>
-      <c r="K24" s="78">
+      <c r="K24" s="76">
         <v>3</v>
       </c>
-      <c r="L24" s="97">
+      <c r="L24" s="95">
         <v>10</v>
       </c>
-      <c r="M24" s="82">
+      <c r="M24" s="80">
         <v>24</v>
       </c>
-      <c r="N24" s="78">
+      <c r="N24" s="76">
         <v>3</v>
       </c>
-      <c r="O24" s="82">
+      <c r="O24" s="80">
         <v>19</v>
       </c>
-      <c r="P24" s="97">
+      <c r="P24" s="95">
         <f>SUM(M24:O24)</f>
         <v>46</v>
       </c>
-      <c r="Q24" s="82">
+      <c r="Q24" s="80">
         <v>20</v>
       </c>
-      <c r="R24" s="78">
+      <c r="R24" s="76">
         <v>2</v>
       </c>
-      <c r="S24" s="67"/>
-      <c r="T24" s="77">
+      <c r="S24" s="76">
+        <v>1</v>
+      </c>
+      <c r="T24" s="75">
         <f>SUM(Q24:S24)</f>
-        <v>22</v>
-      </c>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
+        <v>23</v>
+      </c>
+      <c r="U24" s="65"/>
+      <c r="V24" s="65"/>
       <c r="W24" s="19"/>
-      <c r="X24" s="77">
+      <c r="X24" s="75">
         <f>SUM(U24:W24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="163"/>
-      <c r="C25" s="169" t="s">
+      <c r="B25" s="194"/>
+      <c r="C25" s="199" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="170" t="s">
+      <c r="D25" s="200" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="172" t="s">
+      <c r="E25" s="201" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="173">
+      <c r="F25" s="202">
         <v>120</v>
       </c>
-      <c r="G25" s="174">
+      <c r="G25" s="203">
         <f>SUM(L27,P27,T27,X27)</f>
         <v>48</v>
       </c>
-      <c r="H25" s="122" t="s">
+      <c r="H25" s="118" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="15" t="s">
@@ -3934,18 +4001,18 @@
       <c r="X25" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="Y25" s="54" t="s">
+      <c r="Y25" s="52" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="26" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="163"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="172"/>
-      <c r="F26" s="173"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="122" t="s">
+      <c r="B26" s="194"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="201"/>
+      <c r="F26" s="202"/>
+      <c r="G26" s="204"/>
+      <c r="H26" s="118" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="15">
@@ -4001,81 +4068,81 @@
       </c>
     </row>
     <row r="27" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="163"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="171"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="173"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="122" t="s">
+      <c r="B27" s="194"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="201"/>
+      <c r="F27" s="202"/>
+      <c r="G27" s="204"/>
+      <c r="H27" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="78">
-        <v>0</v>
-      </c>
-      <c r="J27" s="78">
-        <v>0</v>
-      </c>
-      <c r="K27" s="78">
+      <c r="I27" s="76">
+        <v>0</v>
+      </c>
+      <c r="J27" s="76">
+        <v>0</v>
+      </c>
+      <c r="K27" s="76">
         <v>3</v>
       </c>
-      <c r="L27" s="98">
+      <c r="L27" s="96">
         <f>SUM(I27:K27)</f>
         <v>3</v>
       </c>
-      <c r="M27" s="78">
+      <c r="M27" s="76">
         <v>4</v>
       </c>
-      <c r="N27" s="78">
+      <c r="N27" s="76">
         <v>4</v>
       </c>
-      <c r="O27" s="82">
+      <c r="O27" s="80">
         <v>23</v>
       </c>
-      <c r="P27" s="97">
+      <c r="P27" s="95">
         <f>SUM(M27:O27)</f>
         <v>31</v>
       </c>
-      <c r="Q27" s="78">
+      <c r="Q27" s="76">
         <v>4</v>
       </c>
-      <c r="R27" s="78">
+      <c r="R27" s="76">
         <v>3</v>
       </c>
-      <c r="S27" s="78">
+      <c r="S27" s="76">
         <v>7</v>
       </c>
-      <c r="T27" s="56">
+      <c r="T27" s="54">
         <f>SUM(Q27:S27)</f>
         <v>14</v>
       </c>
-      <c r="U27" s="100"/>
-      <c r="V27" s="100"/>
-      <c r="W27" s="100"/>
-      <c r="X27" s="56">
+      <c r="U27" s="98"/>
+      <c r="V27" s="98"/>
+      <c r="W27" s="98"/>
+      <c r="X27" s="54">
         <f>SUM(U27:W27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="163"/>
-      <c r="C28" s="206" t="s">
+      <c r="B28" s="194"/>
+      <c r="C28" s="127" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="207" t="s">
+      <c r="D28" s="168" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="208" t="s">
+      <c r="E28" s="170" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="210">
+      <c r="F28" s="146">
         <v>0.82</v>
       </c>
-      <c r="G28" s="233">
-        <f>R30</f>
-        <v>0.85</v>
-      </c>
-      <c r="H28" s="121" t="s">
+      <c r="G28" s="147">
+        <f>U30</f>
+        <v>0.86</v>
+      </c>
+      <c r="H28" s="117" t="s">
         <v>26</v>
       </c>
       <c r="I28" s="24" t="s">
@@ -4126,18 +4193,18 @@
       <c r="X28" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="Y28" s="54" t="s">
+      <c r="Y28" s="52" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="163"/>
-      <c r="C29" s="164"/>
-      <c r="D29" s="190"/>
-      <c r="E29" s="208"/>
-      <c r="F29" s="210"/>
-      <c r="G29" s="233"/>
-      <c r="H29" s="121" t="s">
+      <c r="B29" s="194"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="169"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="117" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="24">
@@ -4193,80 +4260,82 @@
       </c>
     </row>
     <row r="30" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="163"/>
-      <c r="C30" s="164"/>
-      <c r="D30" s="190"/>
-      <c r="E30" s="208"/>
-      <c r="F30" s="210"/>
-      <c r="G30" s="233"/>
-      <c r="H30" s="121" t="s">
+      <c r="B30" s="194"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="169"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="I30" s="76">
+      <c r="I30" s="74">
         <v>0.72</v>
       </c>
-      <c r="J30" s="75">
+      <c r="J30" s="73">
         <v>0.76</v>
       </c>
-      <c r="K30" s="75">
+      <c r="K30" s="73">
         <v>0.8</v>
       </c>
-      <c r="L30" s="86">
+      <c r="L30" s="84">
         <f>AVERAGE(I30:K30)</f>
         <v>0.76000000000000012</v>
       </c>
-      <c r="M30" s="76">
+      <c r="M30" s="74">
         <v>0.75</v>
       </c>
-      <c r="N30" s="75">
+      <c r="N30" s="73">
         <v>0.84</v>
       </c>
-      <c r="O30" s="76">
+      <c r="O30" s="74">
         <v>0.73</v>
       </c>
-      <c r="P30" s="93">
+      <c r="P30" s="91">
         <f>AVERAGE(M30:O30)</f>
         <v>0.77333333333333332</v>
       </c>
-      <c r="Q30" s="75">
+      <c r="Q30" s="73">
         <v>0.82</v>
       </c>
-      <c r="R30" s="75">
+      <c r="R30" s="73">
         <v>0.85</v>
       </c>
-      <c r="S30" s="75">
+      <c r="S30" s="73">
         <v>0.82</v>
       </c>
-      <c r="T30" s="64">
+      <c r="T30" s="62">
         <f>AVERAGE(Q30:S30)</f>
         <v>0.83</v>
       </c>
-      <c r="U30" s="63"/>
-      <c r="V30" s="63"/>
+      <c r="U30" s="73">
+        <v>0.86</v>
+      </c>
+      <c r="V30" s="61"/>
       <c r="W30" s="19"/>
-      <c r="X30" s="64" t="e">
+      <c r="X30" s="62">
         <f>AVERAGE(U30:W30)</f>
-        <v>#DIV/0!</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="31" spans="2:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="163"/>
-      <c r="C31" s="144" t="s">
+      <c r="B31" s="194"/>
+      <c r="C31" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="171" t="s">
+      <c r="D31" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="156">
+      <c r="E31" s="179">
         <v>0.82</v>
       </c>
-      <c r="F31" s="201">
+      <c r="F31" s="143">
         <v>0.7</v>
       </c>
-      <c r="G31" s="156">
+      <c r="G31" s="179">
         <v>0.83</v>
       </c>
-      <c r="H31" s="122" t="s">
+      <c r="H31" s="118" t="s">
         <v>26</v>
       </c>
       <c r="I31" s="26" t="s">
@@ -4319,13 +4388,13 @@
       </c>
     </row>
     <row r="32" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="163"/>
-      <c r="C32" s="144"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="201"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="122" t="s">
+      <c r="B32" s="194"/>
+      <c r="C32" s="129"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="179"/>
+      <c r="F32" s="143"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="118" t="s">
         <v>27</v>
       </c>
       <c r="I32" s="26">
@@ -4381,13 +4450,13 @@
       </c>
     </row>
     <row r="33" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="163"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="171"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="201"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="122" t="s">
+      <c r="B33" s="194"/>
+      <c r="C33" s="129"/>
+      <c r="D33" s="130"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="118" t="s">
         <v>28</v>
       </c>
       <c r="I33" s="26" t="s">
@@ -4396,10 +4465,10 @@
       <c r="J33" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="K33" s="75">
+      <c r="K33" s="73">
         <v>0.83</v>
       </c>
-      <c r="L33" s="86">
+      <c r="L33" s="84">
         <v>0.83</v>
       </c>
       <c r="M33" s="15" t="s">
@@ -4408,10 +4477,10 @@
       <c r="N33" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="O33" s="75">
+      <c r="O33" s="73">
         <v>0.81</v>
       </c>
-      <c r="P33" s="86">
+      <c r="P33" s="84">
         <v>0.81</v>
       </c>
       <c r="Q33" s="15" t="s">
@@ -4420,37 +4489,37 @@
       <c r="R33" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="S33" s="86">
+      <c r="S33" s="84">
         <v>0.82</v>
       </c>
-      <c r="T33" s="86">
+      <c r="T33" s="84">
         <v>0.82</v>
       </c>
-      <c r="U33" s="49"/>
-      <c r="V33" s="49"/>
+      <c r="U33" s="48"/>
+      <c r="V33" s="48"/>
       <c r="W33" s="15"/>
       <c r="X33" s="33"/>
     </row>
     <row r="34" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="148" t="s">
+      <c r="B34" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="164" t="s">
+      <c r="C34" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="154" t="s">
+      <c r="D34" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="199">
+      <c r="E34" s="152">
         <v>0.77</v>
       </c>
-      <c r="F34" s="210">
+      <c r="F34" s="146">
         <v>0.85</v>
       </c>
-      <c r="G34" s="197">
+      <c r="G34" s="156">
         <v>0.79</v>
       </c>
-      <c r="H34" s="121" t="s">
+      <c r="H34" s="117" t="s">
         <v>26</v>
       </c>
       <c r="I34" s="21">
@@ -4503,13 +4572,13 @@
       </c>
     </row>
     <row r="35" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="149"/>
-      <c r="C35" s="164"/>
-      <c r="D35" s="154"/>
-      <c r="E35" s="199"/>
-      <c r="F35" s="210"/>
-      <c r="G35" s="197"/>
-      <c r="H35" s="121" t="s">
+      <c r="B35" s="187"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="146"/>
+      <c r="G35" s="156"/>
+      <c r="H35" s="117" t="s">
         <v>27</v>
       </c>
       <c r="I35" s="21">
@@ -4562,135 +4631,135 @@
       </c>
     </row>
     <row r="36" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="149"/>
-      <c r="C36" s="165"/>
-      <c r="D36" s="160"/>
-      <c r="E36" s="200"/>
-      <c r="F36" s="210"/>
-      <c r="G36" s="198"/>
-      <c r="H36" s="121" t="s">
+      <c r="B36" s="187"/>
+      <c r="C36" s="195"/>
+      <c r="D36" s="191"/>
+      <c r="E36" s="153"/>
+      <c r="F36" s="146"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="I36" s="75">
+      <c r="I36" s="73">
         <v>0.78</v>
       </c>
-      <c r="J36" s="81">
+      <c r="J36" s="79">
         <v>0.77</v>
       </c>
-      <c r="K36" s="75">
+      <c r="K36" s="73">
         <v>0.79</v>
       </c>
-      <c r="L36" s="86">
+      <c r="L36" s="84">
         <v>0.79</v>
       </c>
-      <c r="M36" s="75">
+      <c r="M36" s="73">
         <v>0.8</v>
       </c>
-      <c r="N36" s="76">
+      <c r="N36" s="74">
         <v>0.8</v>
       </c>
-      <c r="O36" s="81">
+      <c r="O36" s="79">
         <v>0.79600000000000004</v>
       </c>
-      <c r="P36" s="93">
+      <c r="P36" s="91">
         <v>0.8</v>
       </c>
-      <c r="Q36" s="76">
+      <c r="Q36" s="74">
         <v>0.79</v>
       </c>
-      <c r="R36" s="81">
+      <c r="R36" s="79">
         <v>0.8</v>
       </c>
-      <c r="S36" s="81">
+      <c r="S36" s="79">
         <v>0.75800000000000001</v>
       </c>
-      <c r="T36" s="125">
+      <c r="T36" s="115">
         <v>0.76</v>
       </c>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="65"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
+      <c r="W36" s="49"/>
+      <c r="X36" s="63"/>
     </row>
     <row r="37" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="149"/>
-      <c r="C37" s="224" t="s">
+      <c r="B37" s="187"/>
+      <c r="C37" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="227" t="s">
+      <c r="D37" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="214" t="s">
+      <c r="E37" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="215">
-        <v>0.9</v>
-      </c>
-      <c r="G37" s="218">
+      <c r="F37" s="160">
+        <v>0.9</v>
+      </c>
+      <c r="G37" s="163">
         <v>0.6</v>
       </c>
       <c r="H37" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="I37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="M37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="N37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="O37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="P37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="R37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="S37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="T37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="U37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="V37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="W37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="X37" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y37" s="54" t="s">
+      <c r="I37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="O37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="S37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="T37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="U37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="V37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="W37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="X37" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y37" s="52" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="149"/>
-      <c r="C38" s="225"/>
-      <c r="D38" s="228"/>
-      <c r="E38" s="214"/>
-      <c r="F38" s="215"/>
-      <c r="G38" s="218"/>
+      <c r="B38" s="187"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="159"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="163"/>
       <c r="H38" s="39" t="s">
         <v>27</v>
       </c>
@@ -4744,136 +4813,136 @@
       </c>
     </row>
     <row r="39" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="149"/>
-      <c r="C39" s="226"/>
-      <c r="D39" s="228"/>
-      <c r="E39" s="214"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="218"/>
+      <c r="B39" s="187"/>
+      <c r="C39" s="138"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="161"/>
+      <c r="G39" s="163"/>
       <c r="H39" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="I39" s="76">
+      <c r="I39" s="74">
         <v>0.44</v>
       </c>
-      <c r="J39" s="76">
+      <c r="J39" s="74">
         <v>0.44</v>
       </c>
-      <c r="K39" s="75">
+      <c r="K39" s="73">
         <v>0.91</v>
       </c>
-      <c r="L39" s="93">
+      <c r="L39" s="91">
         <v>0.6</v>
       </c>
-      <c r="M39" s="76">
-        <v>0</v>
-      </c>
-      <c r="N39" s="76">
+      <c r="M39" s="74">
+        <v>0</v>
+      </c>
+      <c r="N39" s="74">
         <v>0.6</v>
       </c>
-      <c r="O39" s="76">
+      <c r="O39" s="74">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P39" s="93">
+      <c r="P39" s="91">
         <v>0.4</v>
       </c>
-      <c r="Q39" s="76">
+      <c r="Q39" s="74">
         <v>0.2</v>
       </c>
-      <c r="R39" s="81">
+      <c r="R39" s="79">
         <v>0.7</v>
       </c>
-      <c r="S39" s="81">
+      <c r="S39" s="79">
         <v>0.77</v>
       </c>
-      <c r="T39" s="99">
+      <c r="T39" s="97">
         <v>0.56000000000000005</v>
       </c>
-      <c r="U39" s="59"/>
-      <c r="V39" s="59"/>
-      <c r="W39" s="59"/>
+      <c r="U39" s="57"/>
+      <c r="V39" s="57"/>
+      <c r="W39" s="57"/>
       <c r="X39" s="18"/>
     </row>
     <row r="40" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="149"/>
-      <c r="C40" s="176" t="s">
+      <c r="B40" s="187"/>
+      <c r="C40" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="179" t="s">
+      <c r="D40" s="208" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="180" t="s">
+      <c r="E40" s="209" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="210">
-        <v>0.9</v>
-      </c>
-      <c r="G40" s="212">
+      <c r="F40" s="146">
+        <v>0.9</v>
+      </c>
+      <c r="G40" s="157">
         <v>0.85</v>
       </c>
-      <c r="H40" s="58" t="s">
+      <c r="H40" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="I40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="M40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="N40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="O40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="P40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="R40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="S40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="T40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="U40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="V40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="W40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="X40" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y40" s="54" t="s">
+      <c r="I40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="O40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="P40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="S40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="T40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="U40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="V40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="W40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="X40" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y40" s="52" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="41" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="149"/>
-      <c r="C41" s="177"/>
-      <c r="D41" s="154"/>
-      <c r="E41" s="180"/>
-      <c r="F41" s="210"/>
-      <c r="G41" s="213"/>
-      <c r="H41" s="58" t="s">
+      <c r="B41" s="187"/>
+      <c r="C41" s="206"/>
+      <c r="D41" s="148"/>
+      <c r="E41" s="209"/>
+      <c r="F41" s="146"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="56" t="s">
         <v>27</v>
       </c>
       <c r="I41" s="21">
@@ -4926,135 +4995,135 @@
       </c>
     </row>
     <row r="42" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="149"/>
-      <c r="C42" s="178"/>
-      <c r="D42" s="154"/>
-      <c r="E42" s="180"/>
-      <c r="F42" s="210"/>
-      <c r="G42" s="213"/>
-      <c r="H42" s="58" t="s">
+      <c r="B42" s="187"/>
+      <c r="C42" s="207"/>
+      <c r="D42" s="148"/>
+      <c r="E42" s="209"/>
+      <c r="F42" s="146"/>
+      <c r="G42" s="158"/>
+      <c r="H42" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="I42" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="K42" s="81">
+      <c r="I42" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="79">
         <v>0.85</v>
       </c>
-      <c r="L42" s="99">
+      <c r="L42" s="97">
         <v>0.85</v>
       </c>
-      <c r="M42" s="75">
+      <c r="M42" s="73">
         <v>1</v>
       </c>
-      <c r="N42" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="O42" s="81">
+      <c r="N42" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="O42" s="79">
         <v>0.15</v>
       </c>
-      <c r="P42" s="99">
+      <c r="P42" s="97">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Q42" s="81">
+      <c r="Q42" s="79">
         <v>0.7</v>
       </c>
-      <c r="R42" s="75">
+      <c r="R42" s="73">
         <v>1</v>
       </c>
-      <c r="S42" s="75">
+      <c r="S42" s="73">
         <v>0.92</v>
       </c>
-      <c r="T42" s="99">
+      <c r="T42" s="97">
         <v>0.87</v>
       </c>
-      <c r="U42" s="51"/>
-      <c r="V42" s="51"/>
-      <c r="W42" s="51"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="50"/>
+      <c r="W42" s="50"/>
       <c r="X42" s="13"/>
     </row>
     <row r="43" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="149"/>
-      <c r="C43" s="231" t="s">
+      <c r="B43" s="187"/>
+      <c r="C43" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="227" t="s">
+      <c r="D43" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="214" t="s">
+      <c r="E43" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="F43" s="215">
+      <c r="F43" s="160">
         <v>1</v>
       </c>
-      <c r="G43" s="217">
+      <c r="G43" s="162">
         <v>0.93</v>
       </c>
       <c r="H43" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="I43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="J43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="K43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="L43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="M43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="N43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="O43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="P43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="R43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="S43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="T43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="U43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="V43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="W43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="X43" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y43" s="54" t="s">
+      <c r="I43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="O43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="P43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="R43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="S43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="T43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="U43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="V43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="W43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="X43" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y43" s="52" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="44" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="149"/>
-      <c r="C44" s="232"/>
-      <c r="D44" s="228"/>
-      <c r="E44" s="214"/>
-      <c r="F44" s="215"/>
-      <c r="G44" s="217"/>
+      <c r="B44" s="187"/>
+      <c r="C44" s="145"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="159"/>
+      <c r="F44" s="160"/>
+      <c r="G44" s="162"/>
       <c r="H44" s="39" t="s">
         <v>27</v>
       </c>
@@ -5111,181 +5180,181 @@
       </c>
     </row>
     <row r="45" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="149"/>
-      <c r="C45" s="232"/>
-      <c r="D45" s="228"/>
-      <c r="E45" s="214"/>
-      <c r="F45" s="216"/>
-      <c r="G45" s="217"/>
+      <c r="B45" s="187"/>
+      <c r="C45" s="145"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="159"/>
+      <c r="F45" s="161"/>
+      <c r="G45" s="162"/>
       <c r="H45" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="79" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" s="79" t="s">
-        <v>32</v>
-      </c>
-      <c r="K45" s="81">
+      <c r="I45" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="79">
         <v>0.93</v>
       </c>
-      <c r="L45" s="99">
+      <c r="L45" s="97">
         <v>0.93</v>
       </c>
-      <c r="M45" s="75">
+      <c r="M45" s="73">
         <v>1</v>
       </c>
-      <c r="N45" s="79" t="s">
-        <v>32</v>
-      </c>
-      <c r="O45" s="81">
+      <c r="N45" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" s="79">
         <v>0.98</v>
       </c>
-      <c r="P45" s="99">
+      <c r="P45" s="97">
         <v>0.99</v>
       </c>
-      <c r="Q45" s="81">
+      <c r="Q45" s="79">
         <v>0.95</v>
       </c>
-      <c r="R45" s="75">
+      <c r="R45" s="73">
         <v>1</v>
       </c>
-      <c r="S45" s="75">
+      <c r="S45" s="73">
         <v>1</v>
       </c>
-      <c r="T45" s="99">
+      <c r="T45" s="97">
         <v>0.98</v>
       </c>
-      <c r="U45" s="59"/>
-      <c r="V45" s="59"/>
-      <c r="W45" s="59"/>
+      <c r="U45" s="57"/>
+      <c r="V45" s="57"/>
+      <c r="W45" s="57"/>
       <c r="X45" s="18"/>
     </row>
     <row r="46" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="149"/>
-      <c r="C46" s="164" t="s">
+      <c r="B46" s="187"/>
+      <c r="C46" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="154" t="s">
+      <c r="D46" s="148" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="234">
+      <c r="E46" s="149">
         <v>372</v>
       </c>
-      <c r="F46" s="235">
+      <c r="F46" s="150">
         <v>366</v>
       </c>
-      <c r="G46" s="202">
+      <c r="G46" s="135">
         <v>365</v>
       </c>
-      <c r="H46" s="121" t="s">
+      <c r="H46" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="I46" s="104">
+      <c r="I46" s="102">
         <v>383</v>
       </c>
-      <c r="J46" s="104">
+      <c r="J46" s="102">
         <v>381</v>
       </c>
-      <c r="K46" s="104">
+      <c r="K46" s="102">
         <v>380</v>
       </c>
-      <c r="L46" s="105">
+      <c r="L46" s="103">
         <v>381</v>
       </c>
-      <c r="M46" s="104">
+      <c r="M46" s="102">
         <v>378</v>
       </c>
-      <c r="N46" s="104">
+      <c r="N46" s="102">
         <v>376</v>
       </c>
-      <c r="O46" s="104">
+      <c r="O46" s="102">
         <v>374</v>
       </c>
-      <c r="P46" s="105">
+      <c r="P46" s="103">
         <v>376</v>
       </c>
-      <c r="Q46" s="104">
+      <c r="Q46" s="102">
         <v>372</v>
       </c>
-      <c r="R46" s="104">
+      <c r="R46" s="102">
         <v>370</v>
       </c>
-      <c r="S46" s="104">
+      <c r="S46" s="102">
         <v>371</v>
       </c>
-      <c r="T46" s="105">
+      <c r="T46" s="103">
         <v>371</v>
       </c>
-      <c r="U46" s="104">
+      <c r="U46" s="102">
         <v>372</v>
       </c>
-      <c r="V46" s="104">
+      <c r="V46" s="102">
         <v>371</v>
       </c>
-      <c r="W46" s="104">
+      <c r="W46" s="102">
         <v>371</v>
       </c>
-      <c r="X46" s="105">
+      <c r="X46" s="103">
         <v>371</v>
       </c>
     </row>
     <row r="47" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="149"/>
-      <c r="C47" s="164"/>
-      <c r="D47" s="154"/>
-      <c r="E47" s="234"/>
-      <c r="F47" s="235"/>
-      <c r="G47" s="202"/>
-      <c r="H47" s="121" t="s">
+      <c r="B47" s="187"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="148"/>
+      <c r="E47" s="149"/>
+      <c r="F47" s="150"/>
+      <c r="G47" s="135"/>
+      <c r="H47" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="I47" s="104">
+      <c r="I47" s="102">
         <v>366</v>
       </c>
-      <c r="J47" s="104">
+      <c r="J47" s="102">
         <v>366</v>
       </c>
-      <c r="K47" s="104">
+      <c r="K47" s="102">
         <v>366</v>
       </c>
-      <c r="L47" s="105">
+      <c r="L47" s="103">
         <v>366</v>
       </c>
-      <c r="M47" s="104">
+      <c r="M47" s="102">
         <v>366</v>
       </c>
-      <c r="N47" s="104">
+      <c r="N47" s="102">
         <v>366</v>
       </c>
-      <c r="O47" s="104">
+      <c r="O47" s="102">
         <v>366</v>
       </c>
-      <c r="P47" s="105">
+      <c r="P47" s="103">
         <v>366</v>
       </c>
-      <c r="Q47" s="104">
+      <c r="Q47" s="102">
         <v>366</v>
       </c>
-      <c r="R47" s="104">
+      <c r="R47" s="102">
         <v>366</v>
       </c>
-      <c r="S47" s="104">
+      <c r="S47" s="102">
         <v>366</v>
       </c>
-      <c r="T47" s="105">
+      <c r="T47" s="103">
         <v>366</v>
       </c>
-      <c r="U47" s="104">
+      <c r="U47" s="102">
         <v>366</v>
       </c>
-      <c r="V47" s="104">
+      <c r="V47" s="102">
         <v>366</v>
       </c>
-      <c r="W47" s="104">
+      <c r="W47" s="102">
         <v>366</v>
       </c>
-      <c r="X47" s="105">
+      <c r="X47" s="103">
         <v>366</v>
       </c>
       <c r="Y47" s="7" t="s">
@@ -5293,74 +5362,74 @@
       </c>
     </row>
     <row r="48" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="149"/>
-      <c r="C48" s="164"/>
-      <c r="D48" s="154"/>
-      <c r="E48" s="234"/>
-      <c r="F48" s="235"/>
-      <c r="G48" s="202"/>
-      <c r="H48" s="121" t="s">
+      <c r="B48" s="187"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="148"/>
+      <c r="E48" s="149"/>
+      <c r="F48" s="150"/>
+      <c r="G48" s="135"/>
+      <c r="H48" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="I48" s="74">
+      <c r="I48" s="72">
         <v>379</v>
       </c>
-      <c r="J48" s="74">
+      <c r="J48" s="72">
         <v>373</v>
       </c>
-      <c r="K48" s="74">
+      <c r="K48" s="72">
         <v>380</v>
       </c>
-      <c r="L48" s="94">
+      <c r="L48" s="92">
         <v>377</v>
       </c>
-      <c r="M48" s="74">
+      <c r="M48" s="72">
         <v>377</v>
       </c>
-      <c r="N48" s="85">
+      <c r="N48" s="83">
         <v>365</v>
       </c>
-      <c r="O48" s="85">
+      <c r="O48" s="83">
         <v>365</v>
       </c>
-      <c r="P48" s="94">
+      <c r="P48" s="92">
         <v>369</v>
       </c>
-      <c r="Q48" s="85">
+      <c r="Q48" s="83">
         <v>363</v>
       </c>
-      <c r="R48" s="85">
+      <c r="R48" s="83">
         <v>360</v>
       </c>
-      <c r="S48" s="85">
+      <c r="S48" s="83">
         <v>363</v>
       </c>
-      <c r="T48" s="96">
+      <c r="T48" s="94">
         <v>362</v>
       </c>
-      <c r="U48" s="104"/>
-      <c r="V48" s="104"/>
-      <c r="W48" s="104"/>
-      <c r="X48" s="105"/>
+      <c r="U48" s="102"/>
+      <c r="V48" s="102"/>
+      <c r="W48" s="102"/>
+      <c r="X48" s="103"/>
     </row>
     <row r="49" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="149"/>
-      <c r="C49" s="185" t="s">
+      <c r="B49" s="187"/>
+      <c r="C49" s="174" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="186" t="s">
+      <c r="D49" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="E49" s="187">
+      <c r="E49" s="177">
         <v>0.71</v>
       </c>
-      <c r="F49" s="167">
+      <c r="F49" s="197">
         <v>0.92</v>
       </c>
-      <c r="G49" s="221">
+      <c r="G49" s="131">
         <v>0.72</v>
       </c>
-      <c r="H49" s="122" t="s">
+      <c r="H49" s="118" t="s">
         <v>26</v>
       </c>
       <c r="I49" s="26">
@@ -5413,13 +5482,13 @@
       </c>
     </row>
     <row r="50" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="149"/>
-      <c r="C50" s="144"/>
-      <c r="D50" s="145"/>
-      <c r="E50" s="187"/>
-      <c r="F50" s="167"/>
-      <c r="G50" s="222"/>
-      <c r="H50" s="122" t="s">
+      <c r="B50" s="187"/>
+      <c r="C50" s="129"/>
+      <c r="D50" s="176"/>
+      <c r="E50" s="177"/>
+      <c r="F50" s="197"/>
+      <c r="G50" s="132"/>
+      <c r="H50" s="118" t="s">
         <v>27</v>
       </c>
       <c r="I50" s="26">
@@ -5472,49 +5541,49 @@
       </c>
     </row>
     <row r="51" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="149"/>
-      <c r="C51" s="144"/>
-      <c r="D51" s="145"/>
-      <c r="E51" s="187"/>
-      <c r="F51" s="167"/>
-      <c r="G51" s="222"/>
-      <c r="H51" s="122" t="s">
+      <c r="B51" s="187"/>
+      <c r="C51" s="129"/>
+      <c r="D51" s="176"/>
+      <c r="E51" s="177"/>
+      <c r="F51" s="197"/>
+      <c r="G51" s="132"/>
+      <c r="H51" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="I51" s="76">
+      <c r="I51" s="74">
         <v>0.83</v>
       </c>
-      <c r="J51" s="76">
+      <c r="J51" s="74">
         <v>0.6</v>
       </c>
-      <c r="K51" s="76" t="s">
+      <c r="K51" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="L51" s="93">
+      <c r="L51" s="91">
         <v>0.72</v>
       </c>
-      <c r="M51" s="76">
+      <c r="M51" s="74">
         <v>0.85</v>
       </c>
-      <c r="N51" s="76">
+      <c r="N51" s="74">
         <v>0.89</v>
       </c>
-      <c r="O51" s="76">
+      <c r="O51" s="74">
         <v>0.91</v>
       </c>
-      <c r="P51" s="93">
+      <c r="P51" s="91">
         <v>0.82</v>
       </c>
-      <c r="Q51" s="76">
+      <c r="Q51" s="74">
         <v>0.89</v>
       </c>
-      <c r="R51" s="76">
+      <c r="R51" s="74">
         <v>0.89</v>
       </c>
-      <c r="S51" s="76">
+      <c r="S51" s="74">
         <v>0.88</v>
       </c>
-      <c r="T51" s="76">
+      <c r="T51" s="74">
         <v>0.88</v>
       </c>
       <c r="U51" s="47"/>
@@ -5523,23 +5592,23 @@
       <c r="X51" s="27"/>
     </row>
     <row r="52" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="149"/>
-      <c r="C52" s="164" t="s">
+      <c r="B52" s="187"/>
+      <c r="C52" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="154" t="s">
+      <c r="D52" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="E52" s="168" t="s">
+      <c r="E52" s="198" t="s">
         <v>35</v>
       </c>
-      <c r="F52" s="211" t="s">
+      <c r="F52" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="G52" s="197">
+      <c r="G52" s="156">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H52" s="121" t="s">
+      <c r="H52" s="117" t="s">
         <v>26</v>
       </c>
       <c r="I52" s="24" t="s">
@@ -5590,42 +5659,42 @@
       <c r="X52" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="Y52" s="54" t="s">
+      <c r="Y52" s="52" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="53" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="149"/>
-      <c r="C53" s="164"/>
-      <c r="D53" s="154"/>
-      <c r="E53" s="168"/>
-      <c r="F53" s="194"/>
-      <c r="G53" s="197"/>
-      <c r="H53" s="121" t="s">
+      <c r="B53" s="187"/>
+      <c r="C53" s="128"/>
+      <c r="D53" s="148"/>
+      <c r="E53" s="198"/>
+      <c r="F53" s="155"/>
+      <c r="G53" s="156"/>
+      <c r="H53" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="I53" s="131"/>
-      <c r="J53" s="131"/>
-      <c r="K53" s="131"/>
-      <c r="L53" s="106" t="s">
+      <c r="I53" s="133"/>
+      <c r="J53" s="133"/>
+      <c r="K53" s="133"/>
+      <c r="L53" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="M53" s="131"/>
-      <c r="N53" s="131"/>
-      <c r="O53" s="131"/>
-      <c r="P53" s="106" t="s">
+      <c r="M53" s="133"/>
+      <c r="N53" s="133"/>
+      <c r="O53" s="133"/>
+      <c r="P53" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="Q53" s="131"/>
-      <c r="R53" s="131"/>
-      <c r="S53" s="131"/>
-      <c r="T53" s="106" t="s">
+      <c r="Q53" s="133"/>
+      <c r="R53" s="133"/>
+      <c r="S53" s="133"/>
+      <c r="T53" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="U53" s="131"/>
-      <c r="V53" s="131"/>
-      <c r="W53" s="131"/>
-      <c r="X53" s="106" t="s">
+      <c r="U53" s="133"/>
+      <c r="V53" s="133"/>
+      <c r="W53" s="133"/>
+      <c r="X53" s="104" t="s">
         <v>63</v>
       </c>
       <c r="Y53" s="7" t="s">
@@ -5633,13 +5702,13 @@
       </c>
     </row>
     <row r="54" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="149"/>
-      <c r="C54" s="164"/>
-      <c r="D54" s="154"/>
-      <c r="E54" s="168"/>
-      <c r="F54" s="194"/>
-      <c r="G54" s="197"/>
-      <c r="H54" s="121" t="s">
+      <c r="B54" s="187"/>
+      <c r="C54" s="128"/>
+      <c r="D54" s="148"/>
+      <c r="E54" s="198"/>
+      <c r="F54" s="155"/>
+      <c r="G54" s="156"/>
+      <c r="H54" s="117" t="s">
         <v>28</v>
       </c>
       <c r="I54" s="24" t="s">
@@ -5651,7 +5720,7 @@
       <c r="K54" s="24">
         <v>0.28799999999999998</v>
       </c>
-      <c r="L54" s="93">
+      <c r="L54" s="91">
         <v>0.28999999999999998</v>
       </c>
       <c r="M54" s="24">
@@ -5663,7 +5732,7 @@
       <c r="O54" s="24">
         <v>0.13</v>
       </c>
-      <c r="P54" s="93">
+      <c r="P54" s="91">
         <v>0.16</v>
       </c>
       <c r="Q54" s="24">
@@ -5675,7 +5744,7 @@
       <c r="S54" s="24">
         <v>0.3</v>
       </c>
-      <c r="T54" s="93">
+      <c r="T54" s="91">
         <v>0.24</v>
       </c>
       <c r="U54" s="24"/>
@@ -5684,25 +5753,25 @@
       <c r="X54" s="25"/>
     </row>
     <row r="55" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="149"/>
-      <c r="C55" s="144" t="s">
+      <c r="B55" s="187"/>
+      <c r="C55" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="D55" s="145" t="s">
+      <c r="D55" s="176" t="s">
         <v>68</v>
       </c>
-      <c r="E55" s="146">
+      <c r="E55" s="213">
         <f>X55</f>
         <v>40</v>
       </c>
-      <c r="F55" s="166">
+      <c r="F55" s="196">
         <v>55</v>
       </c>
-      <c r="G55" s="223">
+      <c r="G55" s="134">
         <f>X57</f>
         <v>51</v>
       </c>
-      <c r="H55" s="122" t="s">
+      <c r="H55" s="118" t="s">
         <v>26</v>
       </c>
       <c r="I55" s="15">
@@ -5755,122 +5824,122 @@
       </c>
     </row>
     <row r="56" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="149"/>
-      <c r="C56" s="144"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="166"/>
-      <c r="G56" s="223"/>
-      <c r="H56" s="122" t="s">
+      <c r="B56" s="187"/>
+      <c r="C56" s="129"/>
+      <c r="D56" s="176"/>
+      <c r="E56" s="213"/>
+      <c r="F56" s="196"/>
+      <c r="G56" s="134"/>
+      <c r="H56" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="209" t="s">
-        <v>32</v>
-      </c>
-      <c r="J56" s="209"/>
-      <c r="K56" s="209"/>
+      <c r="I56" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="J56" s="151"/>
+      <c r="K56" s="151"/>
       <c r="L56" s="18">
         <v>13</v>
       </c>
-      <c r="M56" s="209" t="s">
-        <v>32</v>
-      </c>
-      <c r="N56" s="209"/>
-      <c r="O56" s="209"/>
+      <c r="M56" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56" s="151"/>
+      <c r="O56" s="151"/>
       <c r="P56" s="18">
         <v>27</v>
       </c>
-      <c r="Q56" s="209" t="s">
-        <v>32</v>
-      </c>
-      <c r="R56" s="209"/>
-      <c r="S56" s="209"/>
+      <c r="Q56" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="R56" s="151"/>
+      <c r="S56" s="151"/>
       <c r="T56" s="18">
         <v>41</v>
       </c>
-      <c r="U56" s="209" t="s">
-        <v>32</v>
-      </c>
-      <c r="V56" s="209"/>
-      <c r="W56" s="209"/>
+      <c r="U56" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="V56" s="151"/>
+      <c r="W56" s="151"/>
       <c r="X56" s="18">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="149"/>
-      <c r="C57" s="144"/>
-      <c r="D57" s="145"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="166"/>
-      <c r="G57" s="223"/>
-      <c r="H57" s="122" t="s">
+      <c r="B57" s="187"/>
+      <c r="C57" s="129"/>
+      <c r="D57" s="176"/>
+      <c r="E57" s="213"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="134"/>
+      <c r="H57" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="I57" s="107">
-        <v>0</v>
-      </c>
-      <c r="J57" s="107">
-        <v>0</v>
-      </c>
-      <c r="K57" s="107">
+      <c r="I57" s="105">
+        <v>0</v>
+      </c>
+      <c r="J57" s="105">
+        <v>0</v>
+      </c>
+      <c r="K57" s="105">
         <v>17</v>
       </c>
-      <c r="L57" s="88">
+      <c r="L57" s="86">
         <v>17</v>
       </c>
-      <c r="M57" s="107">
+      <c r="M57" s="105">
         <v>25</v>
       </c>
-      <c r="N57" s="107">
-        <v>0</v>
-      </c>
-      <c r="O57" s="107">
-        <v>0</v>
-      </c>
-      <c r="P57" s="112">
+      <c r="N57" s="105">
+        <v>0</v>
+      </c>
+      <c r="O57" s="105">
+        <v>0</v>
+      </c>
+      <c r="P57" s="108">
         <v>42</v>
       </c>
-      <c r="Q57" s="107">
+      <c r="Q57" s="105">
         <v>2</v>
       </c>
-      <c r="R57" s="107">
+      <c r="R57" s="105">
         <v>3</v>
       </c>
-      <c r="S57" s="107">
+      <c r="S57" s="105">
         <v>4</v>
       </c>
-      <c r="T57" s="112">
+      <c r="T57" s="108">
         <v>51</v>
       </c>
-      <c r="U57" s="107"/>
-      <c r="V57" s="107"/>
-      <c r="W57" s="107"/>
-      <c r="X57" s="108">
+      <c r="U57" s="105"/>
+      <c r="V57" s="105"/>
+      <c r="W57" s="105"/>
+      <c r="X57" s="106">
         <f>SUM(T57:W57)</f>
         <v>51</v>
       </c>
     </row>
     <row r="58" spans="2:25" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="148" t="s">
+      <c r="B58" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="157" t="s">
+      <c r="C58" s="188" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="160" t="s">
+      <c r="D58" s="191" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="136">
+      <c r="E58" s="220">
         <v>92.5</v>
       </c>
-      <c r="F58" s="133">
+      <c r="F58" s="227">
         <v>93</v>
       </c>
-      <c r="G58" s="136">
+      <c r="G58" s="220">
         <v>92.5</v>
       </c>
-      <c r="H58" s="121" t="s">
+      <c r="H58" s="117" t="s">
         <v>26</v>
       </c>
       <c r="I58" s="34">
@@ -5926,13 +5995,13 @@
       </c>
     </row>
     <row r="59" spans="2:25" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="149"/>
-      <c r="C59" s="158"/>
-      <c r="D59" s="161"/>
-      <c r="E59" s="137"/>
-      <c r="F59" s="134"/>
-      <c r="G59" s="137"/>
-      <c r="H59" s="121" t="s">
+      <c r="B59" s="187"/>
+      <c r="C59" s="189"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="221"/>
+      <c r="F59" s="228"/>
+      <c r="G59" s="221"/>
+      <c r="H59" s="117" t="s">
         <v>27</v>
       </c>
       <c r="I59" s="19">
@@ -5988,13 +6057,13 @@
       </c>
     </row>
     <row r="60" spans="2:25" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="149"/>
-      <c r="C60" s="159"/>
-      <c r="D60" s="162"/>
-      <c r="E60" s="138"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="138"/>
-      <c r="H60" s="121" t="s">
+      <c r="B60" s="187"/>
+      <c r="C60" s="190"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="222"/>
+      <c r="F60" s="229"/>
+      <c r="G60" s="222"/>
+      <c r="H60" s="117" t="s">
         <v>28</v>
       </c>
       <c r="I60" s="36">
@@ -6012,574 +6081,578 @@
       <c r="S60" s="22"/>
       <c r="T60" s="20"/>
       <c r="U60" s="22"/>
-      <c r="V60" s="101"/>
-      <c r="W60" s="101"/>
+      <c r="V60" s="99"/>
+      <c r="W60" s="99"/>
       <c r="X60" s="20"/>
     </row>
     <row r="61" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="148" t="s">
+      <c r="B61" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="147" t="s">
+      <c r="C61" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="154" t="s">
+      <c r="D61" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="E61" s="155">
+      <c r="E61" s="219">
         <f>L61+P61+T61+X61</f>
         <v>30.187825999999998</v>
       </c>
-      <c r="F61" s="140">
+      <c r="F61" s="231">
         <f>SUM(L62,P62,T62,X62)</f>
         <v>28</v>
       </c>
-      <c r="G61" s="132">
+      <c r="G61" s="226">
         <f>L63+P63+T63+X63</f>
         <v>18.672584000000001</v>
       </c>
-      <c r="H61" s="121" t="s">
+      <c r="H61" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="68">
+      <c r="I61" s="66">
         <v>1.7</v>
       </c>
-      <c r="J61" s="68">
+      <c r="J61" s="66">
         <v>2.5150000000000001</v>
       </c>
-      <c r="K61" s="68">
+      <c r="K61" s="66">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L61" s="69">
+      <c r="L61" s="67">
         <f>K61+J61+I61</f>
         <v>6.5149999999999997</v>
       </c>
-      <c r="M61" s="68">
+      <c r="M61" s="66">
         <v>2.8</v>
       </c>
-      <c r="N61" s="68">
+      <c r="N61" s="66">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O61" s="68">
+      <c r="O61" s="66">
         <v>2.972826</v>
       </c>
-      <c r="P61" s="69">
+      <c r="P61" s="67">
         <f>O61+N61+M61</f>
         <v>7.9728260000000004</v>
       </c>
-      <c r="Q61" s="68">
+      <c r="Q61" s="66">
         <v>2</v>
       </c>
-      <c r="R61" s="68">
+      <c r="R61" s="66">
         <v>2.2999999999999998</v>
       </c>
-      <c r="S61" s="68">
+      <c r="S61" s="66">
         <v>2.7</v>
       </c>
-      <c r="T61" s="69">
+      <c r="T61" s="67">
         <f>S61+R61+Q61</f>
         <v>7</v>
       </c>
-      <c r="U61" s="68">
+      <c r="U61" s="66">
         <v>3.1</v>
       </c>
-      <c r="V61" s="68">
+      <c r="V61" s="66">
         <v>2.6</v>
       </c>
-      <c r="W61" s="68">
+      <c r="W61" s="66">
         <v>3.04</v>
       </c>
-      <c r="X61" s="69">
+      <c r="X61" s="67">
         <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="62" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="149"/>
-      <c r="C62" s="147"/>
-      <c r="D62" s="154"/>
-      <c r="E62" s="155"/>
-      <c r="F62" s="140"/>
-      <c r="G62" s="132"/>
-      <c r="H62" s="121" t="s">
+      <c r="B62" s="187"/>
+      <c r="C62" s="214"/>
+      <c r="D62" s="148"/>
+      <c r="E62" s="219"/>
+      <c r="F62" s="231"/>
+      <c r="G62" s="226"/>
+      <c r="H62" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="I62" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62" s="131"/>
-      <c r="K62" s="131"/>
-      <c r="L62" s="69">
+      <c r="I62" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" s="133"/>
+      <c r="K62" s="133"/>
+      <c r="L62" s="67">
         <v>5</v>
       </c>
-      <c r="M62" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" s="131"/>
-      <c r="O62" s="131"/>
-      <c r="P62" s="69">
+      <c r="M62" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="133"/>
+      <c r="O62" s="133"/>
+      <c r="P62" s="67">
         <v>7</v>
       </c>
-      <c r="Q62" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="R62" s="131"/>
-      <c r="S62" s="131"/>
-      <c r="T62" s="69">
+      <c r="Q62" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="R62" s="133"/>
+      <c r="S62" s="133"/>
+      <c r="T62" s="67">
         <v>7</v>
       </c>
-      <c r="U62" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="V62" s="120"/>
-      <c r="W62" s="120"/>
-      <c r="X62" s="69">
+      <c r="U62" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="V62" s="116"/>
+      <c r="W62" s="116"/>
+      <c r="X62" s="67">
         <v>9</v>
       </c>
     </row>
     <row r="63" spans="2:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="149"/>
-      <c r="C63" s="147"/>
-      <c r="D63" s="154"/>
-      <c r="E63" s="155"/>
-      <c r="F63" s="140"/>
-      <c r="G63" s="132"/>
-      <c r="H63" s="121" t="s">
+      <c r="B63" s="187"/>
+      <c r="C63" s="214"/>
+      <c r="D63" s="148"/>
+      <c r="E63" s="219"/>
+      <c r="F63" s="231"/>
+      <c r="G63" s="226"/>
+      <c r="H63" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="120">
+      <c r="I63" s="116">
         <v>1.333</v>
       </c>
-      <c r="J63" s="120">
+      <c r="J63" s="116">
         <v>1.4</v>
       </c>
-      <c r="K63" s="120">
+      <c r="K63" s="116">
         <v>2.5</v>
       </c>
-      <c r="L63" s="89">
+      <c r="L63" s="87">
         <f>K63+J63+I63</f>
         <v>5.2329999999999997</v>
       </c>
-      <c r="M63" s="120">
+      <c r="M63" s="116">
         <v>1.5</v>
       </c>
-      <c r="N63" s="120">
+      <c r="N63" s="116">
         <v>3.2572839999999998</v>
       </c>
-      <c r="O63" s="120">
+      <c r="O63" s="116">
         <v>1.86</v>
       </c>
-      <c r="P63" s="111">
+      <c r="P63" s="107">
         <f>O63+N63+M63</f>
         <v>6.6172839999999997</v>
       </c>
-      <c r="Q63" s="120">
+      <c r="Q63" s="116">
         <v>2.2623000000000002</v>
       </c>
-      <c r="R63" s="120">
+      <c r="R63" s="116">
         <v>2.5099999999999998</v>
       </c>
-      <c r="S63" s="120">
+      <c r="S63" s="116">
         <v>2.0499999999999998</v>
       </c>
-      <c r="T63" s="111">
+      <c r="T63" s="107">
         <f>S63+R63+Q63</f>
         <v>6.8223000000000003</v>
       </c>
-      <c r="U63" s="120"/>
-      <c r="V63" s="120"/>
-      <c r="W63" s="120"/>
-      <c r="X63" s="90">
+      <c r="U63" s="116"/>
+      <c r="V63" s="116"/>
+      <c r="W63" s="116"/>
+      <c r="X63" s="88">
         <f>W63+V63+U63</f>
         <v>0</v>
       </c>
-      <c r="Y63" s="54" t="s">
+      <c r="Y63" s="52" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="64" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="149"/>
-      <c r="C64" s="141" t="s">
+      <c r="B64" s="187"/>
+      <c r="C64" s="210" t="s">
         <v>77</v>
       </c>
-      <c r="D64" s="142" t="s">
+      <c r="D64" s="211" t="s">
         <v>78</v>
       </c>
-      <c r="E64" s="143">
+      <c r="E64" s="212">
         <f>L64+P64+T64+X64</f>
         <v>-8.4644727175232077</v>
       </c>
-      <c r="F64" s="139">
+      <c r="F64" s="230">
         <f>SUM(L65,P65,T65,X65)</f>
         <v>-7.0189285867816498</v>
       </c>
-      <c r="G64" s="130">
+      <c r="G64" s="234">
         <f>SUM(L66,P66,T66,Q66,X66)</f>
-        <v>-6.3300698065453469</v>
-      </c>
-      <c r="H64" s="123" t="s">
+        <v>-7.7177693521439767</v>
+      </c>
+      <c r="H64" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="I64" s="70">
+      <c r="I64" s="68">
         <v>-0.5</v>
       </c>
-      <c r="J64" s="70">
+      <c r="J64" s="68">
         <v>-0.5</v>
       </c>
-      <c r="K64" s="70">
+      <c r="K64" s="68">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="L64" s="71">
+      <c r="L64" s="69">
         <f t="shared" ref="L64:L69" si="8">SUM(I64:K64)</f>
         <v>-2.1</v>
       </c>
-      <c r="M64" s="70">
+      <c r="M64" s="68">
         <v>-0.5</v>
       </c>
-      <c r="N64" s="70">
+      <c r="N64" s="68">
         <v>0.1</v>
       </c>
-      <c r="O64" s="70">
+      <c r="O64" s="68">
         <v>-1.5</v>
       </c>
-      <c r="P64" s="71">
+      <c r="P64" s="69">
         <f t="shared" ref="P64:P69" si="9">SUM(M64:O64)</f>
         <v>-1.9</v>
       </c>
-      <c r="Q64" s="70">
+      <c r="Q64" s="68">
         <v>-0.9</v>
       </c>
-      <c r="R64" s="70">
+      <c r="R64" s="68">
         <v>-0.83660522126404935</v>
       </c>
-      <c r="S64" s="70">
+      <c r="S64" s="68">
         <v>-0.41</v>
       </c>
-      <c r="T64" s="71">
+      <c r="T64" s="69">
         <f t="shared" ref="T64:T69" si="10">SUM(Q64:S64)</f>
         <v>-2.1466052212640494</v>
       </c>
-      <c r="U64" s="70">
+      <c r="U64" s="68">
         <v>-0.48</v>
       </c>
-      <c r="V64" s="70">
+      <c r="V64" s="68">
         <v>-0.34</v>
       </c>
-      <c r="W64" s="70">
+      <c r="W64" s="68">
         <v>-1.4978674962591589</v>
       </c>
-      <c r="X64" s="71">
+      <c r="X64" s="69">
         <f t="shared" ref="X64:X69" si="11">SUM(U64:W64)</f>
         <v>-2.3178674962591588</v>
       </c>
     </row>
     <row r="65" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="149"/>
-      <c r="C65" s="141"/>
-      <c r="D65" s="142"/>
-      <c r="E65" s="143"/>
-      <c r="F65" s="139"/>
-      <c r="G65" s="130"/>
-      <c r="H65" s="123" t="s">
+      <c r="B65" s="187"/>
+      <c r="C65" s="210"/>
+      <c r="D65" s="211"/>
+      <c r="E65" s="212"/>
+      <c r="F65" s="230"/>
+      <c r="G65" s="234"/>
+      <c r="H65" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I65" s="70">
+      <c r="I65" s="68">
         <v>-0.6</v>
       </c>
-      <c r="J65" s="70">
+      <c r="J65" s="68">
         <v>-0.5</v>
       </c>
-      <c r="K65" s="70">
+      <c r="K65" s="68">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="L65" s="71">
+      <c r="L65" s="69">
         <f t="shared" si="8"/>
         <v>-2.2000000000000002</v>
       </c>
-      <c r="M65" s="70">
+      <c r="M65" s="68">
         <v>-0.8</v>
       </c>
-      <c r="N65" s="70">
+      <c r="N65" s="68">
         <v>-0.5</v>
       </c>
-      <c r="O65" s="70">
+      <c r="O65" s="68">
         <v>-0.7</v>
       </c>
-      <c r="P65" s="71">
+      <c r="P65" s="69">
         <f t="shared" si="9"/>
         <v>-2</v>
       </c>
-      <c r="Q65" s="70">
+      <c r="Q65" s="68">
         <v>-0.4710695833326044</v>
       </c>
-      <c r="R65" s="70">
+      <c r="R65" s="68">
         <v>-0.47785080650561662</v>
       </c>
-      <c r="S65" s="70">
+      <c r="S65" s="68">
         <v>-0.56812301870144577</v>
       </c>
-      <c r="T65" s="71">
+      <c r="T65" s="69">
         <f t="shared" si="10"/>
         <v>-1.5170434085396667</v>
       </c>
-      <c r="U65" s="70">
+      <c r="U65" s="68">
         <v>-0.32641448602076573</v>
       </c>
-      <c r="V65" s="70">
+      <c r="V65" s="68">
         <v>-0.37253694072630583</v>
       </c>
-      <c r="W65" s="70">
+      <c r="W65" s="68">
         <v>-0.60293375149491213</v>
       </c>
-      <c r="X65" s="71">
+      <c r="X65" s="69">
         <f t="shared" si="11"/>
         <v>-1.3018851782419838</v>
       </c>
     </row>
     <row r="66" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="149"/>
-      <c r="C66" s="141"/>
-      <c r="D66" s="142"/>
-      <c r="E66" s="143"/>
-      <c r="F66" s="139"/>
-      <c r="G66" s="130"/>
-      <c r="H66" s="123" t="s">
+      <c r="B66" s="187"/>
+      <c r="C66" s="210"/>
+      <c r="D66" s="211"/>
+      <c r="E66" s="212"/>
+      <c r="F66" s="230"/>
+      <c r="G66" s="234"/>
+      <c r="H66" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="I66" s="80">
+      <c r="I66" s="78">
         <v>-0.8</v>
       </c>
-      <c r="J66" s="80">
+      <c r="J66" s="78">
         <v>-0.8</v>
       </c>
-      <c r="K66" s="87">
+      <c r="K66" s="85">
         <v>-0.5</v>
       </c>
-      <c r="L66" s="95">
+      <c r="L66" s="93">
         <f t="shared" si="8"/>
         <v>-2.1</v>
       </c>
-      <c r="M66" s="87">
+      <c r="M66" s="85">
         <v>-0.6</v>
       </c>
-      <c r="N66" s="80">
+      <c r="N66" s="78">
         <v>-0.9</v>
       </c>
-      <c r="O66" s="87">
+      <c r="O66" s="85">
         <v>-0.27622289841125025</v>
       </c>
-      <c r="P66" s="95">
+      <c r="P66" s="93">
         <f>SUM(M66:O66)</f>
         <v>-1.7762228984112503</v>
       </c>
-      <c r="Q66" s="80">
-        <v>-0.98799805081423986</v>
-      </c>
-      <c r="R66" s="119">
-        <v>-0.47785080650561662</v>
-      </c>
-      <c r="S66" s="70"/>
-      <c r="T66" s="109">
+      <c r="Q66" s="78">
+        <v>-1.0024414133348749</v>
+      </c>
+      <c r="R66" s="114">
+        <v>-7.2116247391932953E-2</v>
+      </c>
+      <c r="S66" s="78">
+        <v>-1.7645473796710434</v>
+      </c>
+      <c r="T66" s="237">
         <f t="shared" si="10"/>
-        <v>-1.4658488573198565</v>
-      </c>
-      <c r="U66" s="70"/>
-      <c r="V66" s="70"/>
-      <c r="W66" s="70"/>
-      <c r="X66" s="109">
+        <v>-2.8391050403978513</v>
+      </c>
+      <c r="U66" s="68"/>
+      <c r="V66" s="68"/>
+      <c r="W66" s="68"/>
+      <c r="X66" s="232">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="149"/>
-      <c r="C67" s="151" t="s">
+      <c r="B67" s="187"/>
+      <c r="C67" s="216" t="s">
         <v>79</v>
       </c>
-      <c r="D67" s="152" t="s">
+      <c r="D67" s="217" t="s">
         <v>78</v>
       </c>
-      <c r="E67" s="153">
+      <c r="E67" s="218">
         <f>L67+P67+T67+X67</f>
         <v>-20.34262829557931</v>
       </c>
-      <c r="F67" s="126">
+      <c r="F67" s="223">
         <f>SUM(L68,P68,T68,X68)</f>
         <v>-24.141371751369434</v>
       </c>
-      <c r="G67" s="129">
+      <c r="G67" s="236">
         <f>SUM(L69,P69,T69,X69)</f>
-        <v>-16.595412480713406</v>
-      </c>
-      <c r="H67" s="124" t="s">
+        <v>-17.543429099999987</v>
+      </c>
+      <c r="H67" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="I67" s="72">
+      <c r="I67" s="70">
         <v>-1.3</v>
       </c>
-      <c r="J67" s="72">
+      <c r="J67" s="70">
         <v>-1.8</v>
       </c>
-      <c r="K67" s="72">
+      <c r="K67" s="70">
         <v>-1.2</v>
       </c>
-      <c r="L67" s="73">
+      <c r="L67" s="71">
         <f t="shared" si="8"/>
         <v>-4.3</v>
       </c>
-      <c r="M67" s="72">
+      <c r="M67" s="70">
         <v>-1.6</v>
       </c>
-      <c r="N67" s="72">
+      <c r="N67" s="70">
         <v>-1.4</v>
       </c>
-      <c r="O67" s="72">
+      <c r="O67" s="70">
         <v>-1.5</v>
       </c>
-      <c r="P67" s="73">
+      <c r="P67" s="71">
         <f t="shared" si="9"/>
         <v>-4.5</v>
       </c>
-      <c r="Q67" s="72">
+      <c r="Q67" s="70">
         <v>-1.91</v>
       </c>
-      <c r="R67" s="72">
+      <c r="R67" s="70">
         <v>-2.3939222677777598</v>
       </c>
-      <c r="S67" s="72">
+      <c r="S67" s="70">
         <v>-2.1</v>
       </c>
-      <c r="T67" s="73">
+      <c r="T67" s="71">
         <f t="shared" si="10"/>
         <v>-6.4039222677777605</v>
       </c>
-      <c r="U67" s="72">
+      <c r="U67" s="70">
         <v>-1.71</v>
       </c>
-      <c r="V67" s="72">
+      <c r="V67" s="70">
         <v>-1.76033753077637</v>
       </c>
-      <c r="W67" s="72">
+      <c r="W67" s="70">
         <v>-1.66836849702518</v>
       </c>
-      <c r="X67" s="73">
+      <c r="X67" s="71">
         <f t="shared" si="11"/>
         <v>-5.1387060278015504</v>
       </c>
     </row>
     <row r="68" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="149"/>
-      <c r="C68" s="151"/>
-      <c r="D68" s="152"/>
-      <c r="E68" s="153"/>
-      <c r="F68" s="127"/>
-      <c r="G68" s="129"/>
-      <c r="H68" s="124" t="s">
+      <c r="B68" s="187"/>
+      <c r="C68" s="216"/>
+      <c r="D68" s="217"/>
+      <c r="E68" s="218"/>
+      <c r="F68" s="224"/>
+      <c r="G68" s="236"/>
+      <c r="H68" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="I68" s="72">
+      <c r="I68" s="70">
         <v>-2.1</v>
       </c>
-      <c r="J68" s="72">
+      <c r="J68" s="70">
         <v>-2.1</v>
       </c>
-      <c r="K68" s="72">
+      <c r="K68" s="70">
         <v>-2.1</v>
       </c>
-      <c r="L68" s="73">
+      <c r="L68" s="71">
         <f t="shared" si="8"/>
         <v>-6.3000000000000007</v>
       </c>
-      <c r="M68" s="72">
+      <c r="M68" s="70">
         <v>-1.7</v>
       </c>
-      <c r="N68" s="72">
+      <c r="N68" s="70">
         <v>-1.7</v>
       </c>
-      <c r="O68" s="72">
+      <c r="O68" s="70">
         <v>-1.7</v>
       </c>
-      <c r="P68" s="73">
+      <c r="P68" s="71">
         <f t="shared" si="9"/>
         <v>-5.0999999999999996</v>
       </c>
-      <c r="Q68" s="72">
+      <c r="Q68" s="70">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="R68" s="72">
+      <c r="R68" s="70">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="S68" s="72">
+      <c r="S68" s="70">
         <v>-2.1922261252282387</v>
       </c>
-      <c r="T68" s="73">
+      <c r="T68" s="71">
         <f t="shared" si="10"/>
         <v>-6.5766783756847165</v>
       </c>
-      <c r="U68" s="72">
+      <c r="U68" s="70">
         <v>-2.0548977918949052</v>
       </c>
-      <c r="V68" s="72">
+      <c r="V68" s="70">
         <v>-2.0548977918949052</v>
       </c>
-      <c r="W68" s="72">
+      <c r="W68" s="70">
         <v>-2.0548977918949052</v>
       </c>
-      <c r="X68" s="73">
+      <c r="X68" s="71">
         <f t="shared" si="11"/>
         <v>-6.1646933756847151</v>
       </c>
     </row>
     <row r="69" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="150"/>
-      <c r="C69" s="151"/>
-      <c r="D69" s="152"/>
-      <c r="E69" s="153"/>
-      <c r="F69" s="128"/>
-      <c r="G69" s="129"/>
-      <c r="H69" s="124" t="s">
+      <c r="B69" s="215"/>
+      <c r="C69" s="216"/>
+      <c r="D69" s="217"/>
+      <c r="E69" s="218"/>
+      <c r="F69" s="225"/>
+      <c r="G69" s="236"/>
+      <c r="H69" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="I69" s="87">
+      <c r="I69" s="85">
         <v>-0.9</v>
       </c>
-      <c r="J69" s="87">
+      <c r="J69" s="85">
         <v>-2</v>
       </c>
-      <c r="K69" s="87">
+      <c r="K69" s="85">
         <v>-2.1</v>
       </c>
-      <c r="L69" s="95">
+      <c r="L69" s="93">
         <f t="shared" si="8"/>
         <v>-5</v>
       </c>
-      <c r="M69" s="87">
+      <c r="M69" s="85">
         <v>-0.3</v>
       </c>
-      <c r="N69" s="80">
+      <c r="N69" s="78">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="O69" s="87">
+      <c r="O69" s="85">
         <v>-1.4</v>
       </c>
-      <c r="P69" s="113">
+      <c r="P69" s="109">
         <f t="shared" si="9"/>
         <v>-6.6</v>
       </c>
-      <c r="Q69" s="80">
-        <v>-2.8031863554851699</v>
-      </c>
-      <c r="R69" s="119">
-        <v>-2.1922261252282387</v>
-      </c>
-      <c r="S69" s="72"/>
-      <c r="T69" s="110">
+      <c r="Q69" s="78">
+        <v>-2.5966383699999951</v>
+      </c>
+      <c r="R69" s="114">
+        <v>-1.9914661799999958</v>
+      </c>
+      <c r="S69" s="114">
+        <v>-1.3553245499999957</v>
+      </c>
+      <c r="T69" s="235">
         <f t="shared" si="10"/>
-        <v>-4.9954124807134086</v>
-      </c>
-      <c r="U69" s="72"/>
-      <c r="V69" s="72"/>
-      <c r="W69" s="72"/>
-      <c r="X69" s="110">
+        <v>-5.943429099999987</v>
+      </c>
+      <c r="U69" s="70"/>
+      <c r="V69" s="70"/>
+      <c r="W69" s="70"/>
+      <c r="X69" s="233">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -6598,6 +6671,109 @@
     </row>
   </sheetData>
   <mergeCells count="127">
+    <mergeCell ref="F67:F69"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="F58:F60"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="B61:B69"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="B19:B33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="B34:B57"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="B4:B18"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="I2:X2"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="U56:W56"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="U53:W53"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="G37:G39"/>
     <mergeCell ref="G19:G21"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="C16:C18"/>
@@ -6622,109 +6798,6 @@
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="F46:F48"/>
     <mergeCell ref="G46:G48"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="U56:W56"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="Q53:S53"/>
-    <mergeCell ref="U53:W53"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="I2:X2"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="B19:B33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="B34:B57"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="B4:B18"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="E64:E66"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="B61:B69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="D67:D69"/>
-    <mergeCell ref="E67:E69"/>
-    <mergeCell ref="D61:D63"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="E58:E60"/>
-    <mergeCell ref="F67:F69"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="M62:O62"/>
-    <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="F58:F60"/>
-    <mergeCell ref="G58:G60"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="F64:F66"/>
-    <mergeCell ref="F61:F63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6776,10 +6849,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="59" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6792,20 +6865,20 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="62"/>
+      <c r="B8" s="60"/>
       <c r="C8" s="30"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="62"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
@@ -6836,13 +6909,13 @@
       <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="59" t="s">
         <v>98</v>
       </c>
       <c r="C12" s="30"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="59" t="s">
         <v>99</v>
       </c>
     </row>
